--- a/Trading Log 2026.xlsx
+++ b/Trading Log 2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2519d2cc87879b8/Desktop/2026 Files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\Python BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1032" documentId="11_F25DC773A252ABDACC1048B631584F605BDE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B52DF1E5-BCA1-49B6-A1DA-83AE8DB248AF}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D13DD85-6D4B-479E-9AB9-FB04E3FE0504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="4" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="210">
   <si>
     <t>Section</t>
   </si>
@@ -639,14 +639,43 @@
   </si>
   <si>
     <t>Capital closed trades cross-referenced across all available reports; duplicate executions are removed and Outcome P/L uses the CLOSED execution’s Rpl Converted value.</t>
+  </si>
+  <si>
+    <t>00353194-0001-54c4-0000-000080fa0902</t>
+  </si>
+  <si>
+    <t>00353194-0001-54c4-0000-000080fa08fb</t>
+  </si>
+  <si>
+    <t>00353194-0001-54c4-0000-000080fa08f6</t>
+  </si>
+  <si>
+    <t>00353194-0001-54c4-0000-000080fa08d3</t>
+  </si>
+  <si>
+    <t>00000355-0001-54c4-0000-000080d93423</t>
+  </si>
+  <si>
+    <t>00396101-0001-54c4-0000-0000813f15ac</t>
+  </si>
+  <si>
+    <t>00000355-0001-54c4-0000-000080d90078</t>
+  </si>
+  <si>
+    <t>00396101-0001-54c4-0000-0000813f04a1</t>
+  </si>
+  <si>
+    <t>00396101-0001-54c4-0000-0000813f04e5</t>
+  </si>
+  <si>
+    <t>00396101-0001-54c4-0000-0000813f04cd</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="8">
-    <numFmt numFmtId="164" formatCode="#,##0.####"/>
+  <numFmts count="7">
     <numFmt numFmtId="165" formatCode="\£#,##0.00;[Red]\-\£#,##0.00;\£0.00"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="0&quot; / 16&quot;"/>
@@ -890,7 +919,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -969,9 +998,6 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -981,12 +1007,6 @@
     </xf>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1011,8 +1031,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1032,59 +1055,14 @@
     <xf numFmtId="0" fontId="15" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="39">
-    <dxf>
-      <numFmt numFmtId="165" formatCode="\£#,##0.00;[Red]\-\£#,##0.00;\£0.00"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="\£#,##0.00;[Red]\-\£#,##0.00;\£0.00"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="\£#,##0.00;[Red]\-\£#,##0.00;\£0.00"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="\£#,##0.00;[Red]\-\£#,##0.00;\£0.00"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="\£#,##0.00;[Red]\-\£#,##0.00;\£0.00"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0.####"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="171" formatCode="dd/mm/yyyy\ hh:mm:ss"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="171" formatCode="dd/mm/yyyy\ hh:mm:ss"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1166,6 +1144,99 @@
       </fill>
     </dxf>
     <dxf>
+      <numFmt numFmtId="170" formatCode="\£#,##0.00;[Red]\-\£#,##0.00"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.000000"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="\£#,##0.00;[Red]\-\£#,##0.00;\£0.00"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="\£#,##0.00;[Red]\-\£#,##0.00;\£0.00"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="\£#,##0.00;[Red]\-\£#,##0.00;\£0.00"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="\£#,##0.00;[Red]\-\£#,##0.00;\£0.00"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="dd/mm/yyyy\ hh:mm:ss"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="dd/mm/yyyy\ hh:mm:ss"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="\£#,##0.00;[Red]\-\£#,##0.00;\£0.00"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="\£#,##0.00;[Red]\-\£#,##0.00"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="\£#,##0.00;[Red]\-\£#,##0.00"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="\£#,##0.00;[Red]\-\£#,##0.00;\£0.00"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment vertical="center" wrapText="1"/>
     </dxf>
     <dxf>
@@ -1194,51 +1265,6 @@
     </dxf>
     <dxf>
       <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="\£#,##0.00;[Red]\-\£#,##0.00"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="\£#,##0.00;[Red]\-\£#,##0.00"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="\£#,##0.00;[Red]\-\£#,##0.00"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="\£#,##0.00;[Red]\-\£#,##0.00;\£0.00"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="169" formatCode="0.000000"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1280,49 +1306,49 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8723A25F-70DD-4018-9AAE-72EBAEFEEE5A}" name="TradingChecklist" displayName="TradingChecklist" ref="A4:E30" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8723A25F-70DD-4018-9AAE-72EBAEFEEE5A}" name="TradingChecklist" displayName="TradingChecklist" ref="A4:E30" totalsRowShown="0" headerRowDxfId="38" dataDxfId="37">
   <autoFilter ref="A4:E30" xr:uid="{8723A25F-70DD-4018-9AAE-72EBAEFEEE5A}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{821CA8CC-FA7E-4394-89A1-972211B17E53}" name="Section" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{1CBE6EF7-5789-4A51-872B-7B964502AF57}" name="Condition" dataDxfId="23"/>
-    <tableColumn id="3" xr3:uid="{4A5168F4-7C45-4286-AEC0-D51E194B61F5}" name="Status" dataDxfId="22"/>
-    <tableColumn id="4" xr3:uid="{20D9AE52-9981-485B-A6E6-827D9834FEF3}" name="Guideline / figure" dataDxfId="21"/>
-    <tableColumn id="5" xr3:uid="{265471C7-1546-40A7-9151-A531208EF1DA}" name="Your notes" dataDxfId="20"/>
+    <tableColumn id="1" xr3:uid="{821CA8CC-FA7E-4394-89A1-972211B17E53}" name="Section" dataDxfId="36"/>
+    <tableColumn id="2" xr3:uid="{1CBE6EF7-5789-4A51-872B-7B964502AF57}" name="Condition" dataDxfId="35"/>
+    <tableColumn id="3" xr3:uid="{4A5168F4-7C45-4286-AEC0-D51E194B61F5}" name="Status" dataDxfId="34"/>
+    <tableColumn id="4" xr3:uid="{20D9AE52-9981-485B-A6E6-827D9834FEF3}" name="Guideline / figure" dataDxfId="33"/>
+    <tableColumn id="5" xr3:uid="{265471C7-1546-40A7-9151-A531208EF1DA}" name="Your notes" dataDxfId="32"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F7F62669-0192-4010-A989-46082A8D2A8F}" name="TradeLog" displayName="TradeLog" ref="A4:V53" totalsRowShown="0" headerRowDxfId="38" dataDxfId="37">
-  <autoFilter ref="A4:V53" xr:uid="{F7F62669-0192-4010-A989-46082A8D2A8F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F7F62669-0192-4010-A989-46082A8D2A8F}" name="TradeLog" displayName="TradeLog" ref="A4:V63" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+  <autoFilter ref="A4:V63" xr:uid="{F7F62669-0192-4010-A989-46082A8D2A8F}"/>
   <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{C7021ECE-8044-45D9-956B-FEB461144659}" name="Trade ID" dataDxfId="36"/>
-    <tableColumn id="2" xr3:uid="{D9579105-80F4-419E-9485-A047857B0F4B}" name="Open Timestamp (UTC)" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{4728173F-0125-4EF5-BA46-BA32162DB22F}" name="Close Timestamp (UTC)" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{DEEA9651-40C1-42E8-9333-29BB942B609C}" name="Ticker" dataDxfId="35"/>
-    <tableColumn id="5" xr3:uid="{0A6E0FA3-1A90-48E2-A625-D255D8C6E1C8}" name="Currency" dataDxfId="34"/>
-    <tableColumn id="6" xr3:uid="{38357F4D-B832-4EA9-9EB6-BA933F1075F7}" name="Direction" dataDxfId="33"/>
-    <tableColumn id="7" xr3:uid="{33740822-6165-4B57-B9C9-678530BB1EC0}" name="Trading Platform" dataDxfId="32"/>
-    <tableColumn id="8" xr3:uid="{34E765F3-F484-4063-BE74-690C3A1B4055}" name="Entry Price" dataDxfId="9"/>
-    <tableColumn id="9" xr3:uid="{E4857188-5946-455B-A90D-BECA70308668}" name="Exit Price" dataDxfId="8"/>
-    <tableColumn id="10" xr3:uid="{825426F3-FF3B-47BC-B751-B5654EE97309}" name="SL" dataDxfId="7"/>
-    <tableColumn id="11" xr3:uid="{E9C1F216-1890-4E0D-888B-B317000B5E92}" name="TP" dataDxfId="6"/>
-    <tableColumn id="12" xr3:uid="{AF2BA964-2A12-45B7-ABB7-525477CD85BE}" name="Position Size" dataDxfId="5"/>
-    <tableColumn id="13" xr3:uid="{807C201C-EF95-494B-A798-D252058D3FEF}" name="Reason for Entry" dataDxfId="31"/>
-    <tableColumn id="14" xr3:uid="{06A0A0CE-6940-4BE5-B34C-AB44F39FAD43}" name="Checklist Passed?" dataDxfId="30"/>
-    <tableColumn id="15" xr3:uid="{BB231E78-399A-4BB3-9202-4425C6DCB66F}" name="Close Source" dataDxfId="29"/>
-    <tableColumn id="16" xr3:uid="{841F24EB-AD9F-4EF7-947C-CEBA705DAD76}" name="Status" dataDxfId="28"/>
-    <tableColumn id="17" xr3:uid="{C2D03972-D982-4A8C-A667-D7BB473A5DFA}" name="Notes" dataDxfId="27"/>
-    <tableColumn id="19" xr3:uid="{C4AFA4D1-43D9-4CDA-A157-218C85E999CA}" name="Fees / Adjustments" dataDxfId="4"/>
-    <tableColumn id="20" xr3:uid="{3747B453-DB01-4E82-8025-B025090B5A0A}" name="Outcome (P/L)" dataDxfId="3"/>
-    <tableColumn id="21" xr3:uid="{47F248F0-5D7E-45EC-B2AF-A2BB771CA7DE}" name="Cumulative P/L" dataDxfId="2">
+    <tableColumn id="1" xr3:uid="{C7021ECE-8044-45D9-956B-FEB461144659}" name="Trade ID" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{D9579105-80F4-419E-9485-A047857B0F4B}" name="Open Timestamp (UTC)" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{4728173F-0125-4EF5-BA46-BA32162DB22F}" name="Close Timestamp (UTC)" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{DEEA9651-40C1-42E8-9333-29BB942B609C}" name="Ticker" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{0A6E0FA3-1A90-48E2-A625-D255D8C6E1C8}" name="Currency" dataDxfId="27"/>
+    <tableColumn id="6" xr3:uid="{38357F4D-B832-4EA9-9EB6-BA933F1075F7}" name="Direction" dataDxfId="26"/>
+    <tableColumn id="7" xr3:uid="{33740822-6165-4B57-B9C9-678530BB1EC0}" name="Trading Platform" dataDxfId="25"/>
+    <tableColumn id="8" xr3:uid="{34E765F3-F484-4063-BE74-690C3A1B4055}" name="Entry Price" dataDxfId="18"/>
+    <tableColumn id="9" xr3:uid="{E4857188-5946-455B-A90D-BECA70308668}" name="Exit Price" dataDxfId="17"/>
+    <tableColumn id="10" xr3:uid="{825426F3-FF3B-47BC-B751-B5654EE97309}" name="SL" dataDxfId="16"/>
+    <tableColumn id="11" xr3:uid="{E9C1F216-1890-4E0D-888B-B317000B5E92}" name="TP" dataDxfId="15"/>
+    <tableColumn id="12" xr3:uid="{AF2BA964-2A12-45B7-ABB7-525477CD85BE}" name="Position Size" dataDxfId="14"/>
+    <tableColumn id="13" xr3:uid="{807C201C-EF95-494B-A798-D252058D3FEF}" name="Reason for Entry" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{06A0A0CE-6940-4BE5-B34C-AB44F39FAD43}" name="Checklist Passed?" dataDxfId="24"/>
+    <tableColumn id="15" xr3:uid="{BB231E78-399A-4BB3-9202-4425C6DCB66F}" name="Close Source" dataDxfId="23"/>
+    <tableColumn id="16" xr3:uid="{841F24EB-AD9F-4EF7-947C-CEBA705DAD76}" name="Status" dataDxfId="22"/>
+    <tableColumn id="17" xr3:uid="{C2D03972-D982-4A8C-A667-D7BB473A5DFA}" name="Notes" dataDxfId="8"/>
+    <tableColumn id="19" xr3:uid="{C4AFA4D1-43D9-4CDA-A157-218C85E999CA}" name="Fees / Adjustments" dataDxfId="21"/>
+    <tableColumn id="20" xr3:uid="{3747B453-DB01-4E82-8025-B025090B5A0A}" name="Outcome (P/L)" dataDxfId="13"/>
+    <tableColumn id="21" xr3:uid="{47F248F0-5D7E-45EC-B2AF-A2BB771CA7DE}" name="Cumulative P/L" dataDxfId="12">
       <calculatedColumnFormula>IF(S5="","",SUM($S$5:S5))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{5C1CBAE9-1077-4830-806F-14CE3BD3A29B}" name="Running Peak" dataDxfId="1">
+    <tableColumn id="22" xr3:uid="{5C1CBAE9-1077-4830-806F-14CE3BD3A29B}" name="Running Peak" dataDxfId="11">
       <calculatedColumnFormula>IF(T5="","",MAX(0,MAX($T$5:T5)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{E3AF948F-A744-4A55-B478-1175642EC3DC}" name="Drawdown" dataDxfId="0">
+    <tableColumn id="23" xr3:uid="{E3AF948F-A744-4A55-B478-1175642EC3DC}" name="Drawdown" dataDxfId="10">
       <calculatedColumnFormula>IF(T5="","",T5-U5)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1601,16 +1627,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="34"/>
+      <c r="B1" s="31"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="35"/>
+      <c r="B2" s="32"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
@@ -1625,56 +1651,56 @@
       </c>
     </row>
     <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="30" t="s">
+      <c r="B5" s="29" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="29" t="s">
+      <c r="A6" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="29" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="30" t="s">
+      <c r="B7" s="29" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="B8" s="30" t="s">
+      <c r="B8" s="29" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="29" t="s">
+      <c r="A9" s="28" t="s">
         <v>180</v>
       </c>
-      <c r="B9" s="30" t="s">
+      <c r="B9" s="29" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="36" t="s">
+      <c r="A11" s="33" t="s">
         <v>182</v>
       </c>
-      <c r="B11" s="36"/>
+      <c r="B11" s="33"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="37" t="s">
+      <c r="A13" s="34" t="s">
         <v>183</v>
       </c>
-      <c r="B13" s="37"/>
+      <c r="B13" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1704,13 +1730,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" s="2" customFormat="1" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
       <c r="F1"/>
       <c r="G1"/>
       <c r="H1"/>
@@ -1758,13 +1784,13 @@
       <c r="AX1"/>
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
     </row>
     <row r="3" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
@@ -1789,11 +1815,11 @@
       <c r="E4" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="G4" s="39" t="s">
+      <c r="G4" s="36" t="s">
         <v>109</v>
       </c>
-      <c r="H4" s="39"/>
-      <c r="I4" s="39"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
     </row>
     <row r="5" spans="1:50" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -1809,12 +1835,12 @@
         <v>58</v>
       </c>
       <c r="E5" s="1"/>
-      <c r="G5" s="40" t="str">
+      <c r="G5" s="37" t="str">
         <f>IF(AND(G8&gt;=12,G9&gt;=3,G10&lt;3),"ENTER LONG",IF(AND(G8&gt;=12,G10&gt;=3,G9&lt;3),"ENTER SHORT","NO ENTRY"))</f>
         <v>NO ENTRY</v>
       </c>
-      <c r="H5" s="40"/>
-      <c r="I5" s="40"/>
+      <c r="H5" s="37"/>
+      <c r="I5" s="37"/>
     </row>
     <row r="6" spans="1:50" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
@@ -1828,9 +1854,9 @@
         <v>60</v>
       </c>
       <c r="E6" s="1"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
+      <c r="G6" s="37"/>
+      <c r="H6" s="37"/>
+      <c r="I6" s="37"/>
     </row>
     <row r="7" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A7" s="6"/>
@@ -1943,11 +1969,11 @@
         <v>66</v>
       </c>
       <c r="E12" s="1"/>
-      <c r="G12" s="38" t="s">
+      <c r="G12" s="35" t="s">
         <v>127</v>
       </c>
-      <c r="H12" s="38"/>
-      <c r="I12" s="38"/>
+      <c r="H12" s="35"/>
+      <c r="I12" s="35"/>
     </row>
     <row r="13" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A13" s="6"/>
@@ -2203,31 +2229,31 @@
       <c r="E31" s="5"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="41" t="s">
+      <c r="A32" s="38" t="s">
         <v>84</v>
       </c>
-      <c r="B32" s="41"/>
-      <c r="C32" s="41"/>
-      <c r="D32" s="41"/>
-      <c r="E32" s="41"/>
+      <c r="B32" s="38"/>
+      <c r="C32" s="38"/>
+      <c r="D32" s="38"/>
+      <c r="E32" s="38"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="42" t="s">
+      <c r="A33" s="39" t="s">
         <v>124</v>
       </c>
-      <c r="B33" s="42"/>
-      <c r="C33" s="42"/>
-      <c r="D33" s="42"/>
-      <c r="E33" s="42"/>
+      <c r="B33" s="39"/>
+      <c r="C33" s="39"/>
+      <c r="D33" s="39"/>
+      <c r="E33" s="39"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="38" t="s">
+      <c r="A34" s="35" t="s">
         <v>125</v>
       </c>
-      <c r="B34" s="38"/>
-      <c r="C34" s="38"/>
-      <c r="D34" s="38"/>
-      <c r="E34" s="38"/>
+      <c r="B34" s="35"/>
+      <c r="C34" s="35"/>
+      <c r="D34" s="35"/>
+      <c r="E34" s="35"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35"/>
@@ -2751,18 +2777,18 @@
     <mergeCell ref="A33:E33"/>
   </mergeCells>
   <conditionalFormatting sqref="C5:C30">
-    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5:I6">
-    <cfRule type="expression" dxfId="18" priority="2">
+    <cfRule type="expression" dxfId="6" priority="2">
       <formula>G5="ENTER LONG"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="3">
+    <cfRule type="expression" dxfId="5" priority="3">
       <formula>G5="ENTER SHORT"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="4">
+    <cfRule type="expression" dxfId="4" priority="4">
       <formula>G5="NO ENTRY"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2775,81 +2801,80 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFBDF1B9-0C0F-447C-99C3-2032A6757813}">
-  <dimension ref="A1:W524"/>
+  <dimension ref="A1:W523"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="3" width="24" customWidth="1"/>
-    <col min="4" max="6" width="12.42578125" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="9" width="14.28515625" customWidth="1"/>
-    <col min="10" max="11" width="13.28515625" customWidth="1"/>
-    <col min="12" max="12" width="15.28515625" customWidth="1"/>
-    <col min="13" max="13" width="17.85546875" customWidth="1"/>
-    <col min="14" max="14" width="18.7109375" customWidth="1"/>
-    <col min="15" max="15" width="15.28515625" customWidth="1"/>
-    <col min="16" max="16" width="12.42578125" customWidth="1"/>
-    <col min="17" max="17" width="28.5703125" customWidth="1"/>
-    <col min="18" max="18" width="17.140625" customWidth="1"/>
-    <col min="19" max="19" width="20.42578125" customWidth="1"/>
-    <col min="20" max="20" width="17.140625" customWidth="1"/>
-    <col min="21" max="21" width="18.140625" customWidth="1"/>
-    <col min="22" max="22" width="17.140625" customWidth="1"/>
+    <col min="1" max="1" width="41.85546875" customWidth="1"/>
+    <col min="2" max="3" width="23.85546875" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" customWidth="1"/>
+    <col min="5" max="6" width="12.42578125" customWidth="1"/>
+    <col min="7" max="7" width="16.140625" customWidth="1"/>
+    <col min="8" max="11" width="13.7109375" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" customWidth="1"/>
+    <col min="13" max="13" width="28.5703125" customWidth="1"/>
+    <col min="14" max="14" width="18.140625" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" customWidth="1"/>
+    <col min="16" max="16" width="13.28515625" customWidth="1"/>
+    <col min="17" max="17" width="34.28515625" customWidth="1"/>
+    <col min="18" max="18" width="20" customWidth="1"/>
+    <col min="19" max="19" width="17.140625" customWidth="1"/>
+    <col min="20" max="20" width="18.140625" customWidth="1"/>
+    <col min="21" max="22" width="17.140625" customWidth="1"/>
     <col min="23" max="23" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="33"/>
-      <c r="R1" s="33"/>
-      <c r="S1" s="33"/>
-      <c r="T1" s="33"/>
-      <c r="U1" s="33"/>
-      <c r="V1" s="33"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="41"/>
+      <c r="P1" s="41"/>
+      <c r="Q1" s="41"/>
+      <c r="R1" s="41"/>
+      <c r="S1" s="41"/>
+      <c r="T1" s="41"/>
+      <c r="U1" s="41"/>
+      <c r="V1" s="41"/>
       <c r="W1" s="20"/>
     </row>
     <row r="2" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="40" t="s">
         <v>199</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
-      <c r="N2" s="32"/>
-      <c r="O2" s="32"/>
-      <c r="P2" s="32"/>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="32"/>
-      <c r="S2" s="32"/>
-      <c r="T2" s="32"/>
-      <c r="U2" s="32"/>
-      <c r="V2" s="32"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
+      <c r="M2" s="40"/>
+      <c r="N2" s="40"/>
+      <c r="O2" s="40"/>
+      <c r="P2" s="40"/>
+      <c r="Q2" s="40"/>
+      <c r="R2" s="40"/>
+      <c r="S2" s="40"/>
+      <c r="T2" s="40"/>
+      <c r="U2" s="40"/>
+      <c r="V2" s="40"/>
       <c r="W2" s="21"/>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
@@ -2939,13 +2964,13 @@
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>171</v>
+        <v>209</v>
       </c>
       <c r="B5" s="24">
-        <v>46245.611831921298</v>
+        <v>46244.790372083335</v>
       </c>
       <c r="C5" s="24">
-        <v>46245.617763333328</v>
+        <v>46244.791148553239</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>145</v>
@@ -2960,55 +2985,51 @@
         <v>105</v>
       </c>
       <c r="H5" s="25">
-        <v>218.93</v>
+        <v>219.01</v>
       </c>
       <c r="I5" s="25">
-        <v>219.51</v>
-      </c>
-      <c r="J5" s="26">
-        <v>219.51</v>
-      </c>
+        <v>219.06</v>
+      </c>
+      <c r="J5" s="26"/>
       <c r="K5" s="26"/>
-      <c r="L5" s="27">
-        <v>1</v>
+      <c r="L5" s="26">
+        <v>0.5</v>
       </c>
       <c r="M5" s="17"/>
-      <c r="N5" s="16" t="s">
-        <v>108</v>
-      </c>
+      <c r="N5" s="16"/>
       <c r="O5" s="18" t="s">
-        <v>31</v>
+        <v>132</v>
       </c>
       <c r="P5" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="Q5" s="31"/>
-      <c r="R5" s="28"/>
-      <c r="S5" s="28">
-        <v>-0.43</v>
-      </c>
-      <c r="T5" s="28">
+      <c r="Q5" s="30"/>
+      <c r="R5" s="27"/>
+      <c r="S5" s="27">
+        <v>-0.02</v>
+      </c>
+      <c r="T5" s="27">
         <f>IF(S5="","",SUM($S$5:S5))</f>
-        <v>-0.43</v>
-      </c>
-      <c r="U5" s="28">
+        <v>-0.02</v>
+      </c>
+      <c r="U5" s="27">
         <f>IF(T5="","",MAX(0,MAX($T$5:T5)))</f>
         <v>0</v>
       </c>
-      <c r="V5" s="28">
+      <c r="V5" s="27">
         <f>IF(T5="","",T5-U5)</f>
-        <v>-0.43</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>170</v>
+        <v>208</v>
       </c>
       <c r="B6" s="24">
-        <v>46245.724190497684</v>
+        <v>46244.80452153935</v>
       </c>
       <c r="C6" s="24">
-        <v>46245.724275046297</v>
+        <v>46244.805508124999</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>145</v>
@@ -3017,61 +3038,55 @@
         <v>129</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G6" s="8" t="s">
         <v>105</v>
       </c>
       <c r="H6" s="25">
-        <v>217.32</v>
+        <v>219.08</v>
       </c>
       <c r="I6" s="25">
-        <v>217.25</v>
-      </c>
-      <c r="J6" s="26">
-        <v>123</v>
-      </c>
+        <v>218.98</v>
+      </c>
+      <c r="J6" s="26"/>
       <c r="K6" s="26"/>
-      <c r="L6" s="27">
-        <v>1</v>
+      <c r="L6" s="26">
+        <v>0.5</v>
       </c>
       <c r="M6" s="17"/>
-      <c r="N6" s="16" t="s">
-        <v>108</v>
-      </c>
+      <c r="N6" s="16"/>
       <c r="O6" s="18" t="s">
         <v>132</v>
       </c>
       <c r="P6" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="Q6" s="31"/>
-      <c r="R6" s="28"/>
-      <c r="S6" s="28">
-        <v>-0.05</v>
-      </c>
-      <c r="T6" s="28">
+      <c r="Q6" s="30"/>
+      <c r="R6" s="27"/>
+      <c r="S6" s="27">
+        <v>0.04</v>
+      </c>
+      <c r="T6" s="27">
         <f>IF(S6="","",SUM($S$5:S6))</f>
-        <v>-0.48</v>
-      </c>
-      <c r="U6" s="28">
+        <v>0.02</v>
+      </c>
+      <c r="U6" s="27">
         <f>IF(T6="","",MAX(0,MAX($T$5:T6)))</f>
+        <v>0.02</v>
+      </c>
+      <c r="V6" s="27">
+        <f>IF(T6="","",T6-U6)</f>
         <v>0</v>
-      </c>
-      <c r="V6" s="28">
-        <f t="shared" ref="V6:V53" si="0">IF(T6="","",T6-U6)</f>
-        <v>-0.48</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="B7" s="24">
-        <v>46245.729444849538</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="B7" s="24"/>
       <c r="C7" s="24">
-        <v>46245.729543182868</v>
+        <v>46244.831266458335</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>145</v>
@@ -3080,124 +3095,116 @@
         <v>129</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="H7" s="25">
-        <v>217.37</v>
-      </c>
+      <c r="H7" s="25"/>
       <c r="I7" s="25">
-        <v>217.18</v>
-      </c>
-      <c r="J7" s="26">
-        <v>123</v>
-      </c>
+        <v>217.55</v>
+      </c>
+      <c r="J7" s="26"/>
       <c r="K7" s="26"/>
-      <c r="L7" s="27">
+      <c r="L7" s="26">
         <v>1</v>
       </c>
       <c r="M7" s="17"/>
-      <c r="N7" s="16" t="s">
-        <v>108</v>
-      </c>
+      <c r="N7" s="16"/>
       <c r="O7" s="18" t="s">
         <v>132</v>
       </c>
       <c r="P7" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="Q7" s="31"/>
-      <c r="R7" s="28"/>
-      <c r="S7" s="28">
-        <v>-0.14000000000000001</v>
-      </c>
-      <c r="T7" s="28">
+      <c r="Q7" s="30"/>
+      <c r="R7" s="27"/>
+      <c r="S7" s="27">
+        <v>0.62</v>
+      </c>
+      <c r="T7" s="27">
         <f>IF(S7="","",SUM($S$5:S7))</f>
-        <v>-0.62</v>
-      </c>
-      <c r="U7" s="28">
+        <v>0.64</v>
+      </c>
+      <c r="U7" s="27">
         <f>IF(T7="","",MAX(0,MAX($T$5:T7)))</f>
+        <v>0.64</v>
+      </c>
+      <c r="V7" s="27">
+        <f>IF(T7="","",T7-U7)</f>
         <v>0</v>
-      </c>
-      <c r="V7" s="28">
-        <f t="shared" si="0"/>
-        <v>-0.62</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B8" s="24">
-        <v>46245.784776412038</v>
+        <v>46245.518400844907</v>
       </c>
       <c r="C8" s="24">
-        <v>46245.79710653935</v>
+        <v>46246.578073483797</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>129</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>105</v>
       </c>
       <c r="H8" s="25">
-        <v>503.68</v>
+        <v>172.71</v>
       </c>
       <c r="I8" s="26">
-        <v>502.48</v>
-      </c>
-      <c r="J8" s="26">
-        <v>502.5</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="J8" s="26"/>
       <c r="K8" s="26"/>
-      <c r="L8" s="27">
-        <v>1</v>
+      <c r="L8" s="26">
+        <v>2.5</v>
       </c>
       <c r="M8" s="17"/>
       <c r="N8" s="16" t="s">
         <v>108</v>
       </c>
       <c r="O8" s="18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P8" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="Q8" s="31"/>
-      <c r="R8" s="28"/>
-      <c r="S8" s="28">
-        <v>-0.89</v>
-      </c>
-      <c r="T8" s="28">
+      <c r="Q8" s="30"/>
+      <c r="R8" s="27"/>
+      <c r="S8" s="27">
+        <v>4.97</v>
+      </c>
+      <c r="T8" s="27">
         <f>IF(S8="","",SUM($S$5:S8))</f>
-        <v>-1.51</v>
-      </c>
-      <c r="U8" s="28">
+        <v>5.6099999999999994</v>
+      </c>
+      <c r="U8" s="27">
         <f>IF(T8="","",MAX(0,MAX($T$5:T8)))</f>
+        <v>5.6099999999999994</v>
+      </c>
+      <c r="V8" s="27">
+        <f>IF(T8="","",T8-U8)</f>
         <v>0</v>
-      </c>
-      <c r="V8" s="28">
-        <f t="shared" si="0"/>
-        <v>-1.51</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B9" s="24">
-        <v>46245.816002962965</v>
+        <v>46245.611831921298</v>
       </c>
       <c r="C9" s="24">
-        <v>46245.825537546298</v>
+        <v>46245.617763333328</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>145</v>
@@ -3206,23 +3213,23 @@
         <v>129</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>105</v>
       </c>
       <c r="H9" s="25">
-        <v>218.04</v>
+        <v>218.93</v>
       </c>
       <c r="I9" s="26">
-        <v>217.22</v>
+        <v>219.51</v>
       </c>
       <c r="J9" s="26">
-        <v>217.22</v>
+        <v>219.51</v>
       </c>
       <c r="K9" s="26"/>
-      <c r="L9" s="27">
-        <v>0.4</v>
+      <c r="L9" s="26">
+        <v>1</v>
       </c>
       <c r="M9" s="17"/>
       <c r="N9" s="16" t="s">
@@ -3234,36 +3241,36 @@
       <c r="P9" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="Q9" s="31"/>
-      <c r="R9" s="28"/>
-      <c r="S9" s="28">
-        <v>-0.24</v>
-      </c>
-      <c r="T9" s="28">
+      <c r="Q9" s="30"/>
+      <c r="R9" s="27"/>
+      <c r="S9" s="27">
+        <v>-0.43</v>
+      </c>
+      <c r="T9" s="27">
         <f>IF(S9="","",SUM($S$5:S9))</f>
-        <v>-1.75</v>
-      </c>
-      <c r="U9" s="28">
+        <v>5.18</v>
+      </c>
+      <c r="U9" s="27">
         <f>IF(T9="","",MAX(0,MAX($T$5:T9)))</f>
-        <v>0</v>
-      </c>
-      <c r="V9" s="28">
-        <f t="shared" si="0"/>
-        <v>-1.75</v>
+        <v>5.6099999999999994</v>
+      </c>
+      <c r="V9" s="27">
+        <f>IF(T9="","",T9-U9)</f>
+        <v>-0.42999999999999972</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B10" s="24">
-        <v>46245.858458553237</v>
+        <v>46245.724190497684</v>
       </c>
       <c r="C10" s="24">
-        <v>46246.522651608801</v>
+        <v>46245.724275046297</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>37</v>
+        <v>145</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>129</v>
@@ -3275,58 +3282,58 @@
         <v>105</v>
       </c>
       <c r="H10" s="25">
-        <v>866.65</v>
+        <v>217.32</v>
       </c>
       <c r="I10" s="26">
-        <v>901.18</v>
+        <v>217.25</v>
       </c>
       <c r="J10" s="26">
-        <v>849.3</v>
+        <v>123</v>
       </c>
       <c r="K10" s="26"/>
-      <c r="L10" s="27">
-        <v>0.47</v>
+      <c r="L10" s="26">
+        <v>1</v>
       </c>
       <c r="M10" s="17"/>
       <c r="N10" s="16" t="s">
         <v>108</v>
       </c>
       <c r="O10" s="18" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="P10" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="Q10" s="31"/>
-      <c r="R10" s="28"/>
-      <c r="S10" s="28">
-        <v>11.92</v>
-      </c>
-      <c r="T10" s="28">
+      <c r="Q10" s="30"/>
+      <c r="R10" s="27"/>
+      <c r="S10" s="27">
+        <v>-0.05</v>
+      </c>
+      <c r="T10" s="27">
         <f>IF(S10="","",SUM($S$5:S10))</f>
-        <v>10.17</v>
-      </c>
-      <c r="U10" s="28">
+        <v>5.13</v>
+      </c>
+      <c r="U10" s="27">
         <f>IF(T10="","",MAX(0,MAX($T$5:T10)))</f>
-        <v>10.17</v>
-      </c>
-      <c r="V10" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5.6099999999999994</v>
+      </c>
+      <c r="V10" s="27">
+        <f>IF(T10="","",T10-U10)</f>
+        <v>-0.47999999999999954</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B11" s="24">
-        <v>46245.876891678243</v>
+        <v>46245.729444849538</v>
       </c>
       <c r="C11" s="24">
-        <v>46246.522651608801</v>
+        <v>46245.729543182868</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>37</v>
+        <v>145</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>129</v>
@@ -3338,60 +3345,58 @@
         <v>105</v>
       </c>
       <c r="H11" s="25">
-        <v>866.5</v>
+        <v>217.37</v>
       </c>
       <c r="I11" s="26">
-        <v>901.18</v>
+        <v>217.18</v>
       </c>
       <c r="J11" s="26">
-        <v>849.41</v>
-      </c>
-      <c r="K11" s="26">
-        <v>900.68</v>
-      </c>
-      <c r="L11" s="27">
-        <v>0.3</v>
+        <v>123</v>
+      </c>
+      <c r="K11" s="26"/>
+      <c r="L11" s="26">
+        <v>1</v>
       </c>
       <c r="M11" s="17"/>
       <c r="N11" s="16" t="s">
         <v>108</v>
       </c>
       <c r="O11" s="18" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="P11" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="Q11" s="31"/>
-      <c r="R11" s="28"/>
-      <c r="S11" s="28">
-        <v>7.64</v>
-      </c>
-      <c r="T11" s="28">
+      <c r="Q11" s="30"/>
+      <c r="R11" s="27"/>
+      <c r="S11" s="27">
+        <v>-0.14000000000000001</v>
+      </c>
+      <c r="T11" s="27">
         <f>IF(S11="","",SUM($S$5:S11))</f>
-        <v>17.809999999999999</v>
-      </c>
-      <c r="U11" s="28">
+        <v>4.99</v>
+      </c>
+      <c r="U11" s="27">
         <f>IF(T11="","",MAX(0,MAX($T$5:T11)))</f>
-        <v>17.809999999999999</v>
-      </c>
-      <c r="V11" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5.6099999999999994</v>
+      </c>
+      <c r="V11" s="27">
+        <f>IF(T11="","",T11-U11)</f>
+        <v>-0.61999999999999922</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B12" s="24">
-        <v>46246.56257130787</v>
+        <v>46245.784776412038</v>
       </c>
       <c r="C12" s="24">
-        <v>46246.578073263889</v>
+        <v>46245.79710653935</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="E12" s="8" t="s">
         <v>129</v>
@@ -3403,19 +3408,17 @@
         <v>105</v>
       </c>
       <c r="H12" s="25">
-        <v>173.73</v>
+        <v>503.68</v>
       </c>
       <c r="I12" s="26">
-        <v>169.87</v>
+        <v>502.48</v>
       </c>
       <c r="J12" s="26">
-        <v>169.89</v>
-      </c>
-      <c r="K12" s="26">
-        <v>180.28</v>
-      </c>
-      <c r="L12" s="27">
-        <v>4</v>
+        <v>502.5</v>
+      </c>
+      <c r="K12" s="26"/>
+      <c r="L12" s="26">
+        <v>1</v>
       </c>
       <c r="M12" s="17"/>
       <c r="N12" s="16" t="s">
@@ -3427,94 +3430,96 @@
       <c r="P12" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="Q12" s="31"/>
-      <c r="R12" s="28"/>
-      <c r="S12" s="28">
-        <v>-11.49</v>
-      </c>
-      <c r="T12" s="28">
+      <c r="Q12" s="30"/>
+      <c r="R12" s="27"/>
+      <c r="S12" s="27">
+        <v>-0.89</v>
+      </c>
+      <c r="T12" s="27">
         <f>IF(S12="","",SUM($S$5:S12))</f>
-        <v>6.3199999999999985</v>
-      </c>
-      <c r="U12" s="28">
+        <v>4.1000000000000005</v>
+      </c>
+      <c r="U12" s="27">
         <f>IF(T12="","",MAX(0,MAX($T$5:T12)))</f>
-        <v>17.809999999999999</v>
-      </c>
-      <c r="V12" s="28">
-        <f t="shared" si="0"/>
-        <v>-11.49</v>
+        <v>5.6099999999999994</v>
+      </c>
+      <c r="V12" s="27">
+        <f>IF(T12="","",T12-U12)</f>
+        <v>-1.5099999999999989</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B13" s="24">
-        <v>46245.518400844907</v>
+        <v>46245.816002962965</v>
       </c>
       <c r="C13" s="24">
-        <v>46246.578073483797</v>
+        <v>46245.825537546298</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>129</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G13" s="8" t="s">
         <v>105</v>
       </c>
       <c r="H13" s="25">
-        <v>172.71</v>
+        <v>218.04</v>
       </c>
       <c r="I13" s="26">
-        <v>170</v>
-      </c>
-      <c r="J13" s="26"/>
+        <v>217.22</v>
+      </c>
+      <c r="J13" s="26">
+        <v>217.22</v>
+      </c>
       <c r="K13" s="26"/>
-      <c r="L13" s="27">
-        <v>2.5</v>
+      <c r="L13" s="26">
+        <v>0.4</v>
       </c>
       <c r="M13" s="17"/>
       <c r="N13" s="16" t="s">
         <v>108</v>
       </c>
       <c r="O13" s="18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P13" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="Q13" s="31"/>
-      <c r="R13" s="28"/>
-      <c r="S13" s="28">
-        <v>4.97</v>
-      </c>
-      <c r="T13" s="28">
+      <c r="Q13" s="30"/>
+      <c r="R13" s="27"/>
+      <c r="S13" s="27">
+        <v>-0.24</v>
+      </c>
+      <c r="T13" s="27">
         <f>IF(S13="","",SUM($S$5:S13))</f>
-        <v>11.29</v>
-      </c>
-      <c r="U13" s="28">
+        <v>3.8600000000000003</v>
+      </c>
+      <c r="U13" s="27">
         <f>IF(T13="","",MAX(0,MAX($T$5:T13)))</f>
-        <v>17.809999999999999</v>
-      </c>
-      <c r="V13" s="28">
-        <f t="shared" si="0"/>
-        <v>-6.52</v>
+        <v>5.6099999999999994</v>
+      </c>
+      <c r="V13" s="27">
+        <f>IF(T13="","",T13-U13)</f>
+        <v>-1.7499999999999991</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="B14" s="24">
-        <v>46245.878077534726</v>
+        <v>46245.833421516203</v>
       </c>
       <c r="C14" s="24">
-        <v>46246.584874374996</v>
+        <v>46246.652417442128</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>136</v>
@@ -3529,60 +3534,58 @@
         <v>105</v>
       </c>
       <c r="H14" s="25">
-        <v>502.25</v>
+        <v>503.85</v>
       </c>
       <c r="I14" s="26">
-        <v>492.17</v>
+        <v>492.76</v>
       </c>
       <c r="J14" s="26">
-        <v>492.21</v>
-      </c>
-      <c r="K14" s="26">
-        <v>522.32000000000005</v>
-      </c>
-      <c r="L14" s="27">
-        <v>0.32</v>
+        <v>400</v>
+      </c>
+      <c r="K14" s="26"/>
+      <c r="L14" s="26">
+        <v>0.38</v>
       </c>
       <c r="M14" s="17"/>
       <c r="N14" s="16" t="s">
         <v>108</v>
       </c>
       <c r="O14" s="18" t="s">
-        <v>31</v>
+        <v>132</v>
       </c>
       <c r="P14" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="Q14" s="31"/>
-      <c r="R14" s="28"/>
-      <c r="S14" s="28">
-        <v>-2.4</v>
-      </c>
-      <c r="T14" s="28">
+      <c r="Q14" s="30"/>
+      <c r="R14" s="27"/>
+      <c r="S14" s="27">
+        <v>-3.14</v>
+      </c>
+      <c r="T14" s="27">
         <f>IF(S14="","",SUM($S$5:S14))</f>
-        <v>8.8899999999999988</v>
-      </c>
-      <c r="U14" s="28">
+        <v>0.7200000000000002</v>
+      </c>
+      <c r="U14" s="27">
         <f>IF(T14="","",MAX(0,MAX($T$5:T14)))</f>
-        <v>17.809999999999999</v>
-      </c>
-      <c r="V14" s="28">
-        <f t="shared" si="0"/>
-        <v>-8.92</v>
+        <v>5.6099999999999994</v>
+      </c>
+      <c r="V14" s="27">
+        <f>IF(T14="","",T14-U14)</f>
+        <v>-4.8899999999999988</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B15" s="24">
-        <v>46246.524338668984</v>
+        <v>46245.858458553237</v>
       </c>
       <c r="C15" s="24">
-        <v>46246.649064293983</v>
+        <v>46246.522651608801</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>145</v>
+        <v>37</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>129</v>
@@ -3594,60 +3597,58 @@
         <v>105</v>
       </c>
       <c r="H15" s="25">
-        <v>220.1</v>
+        <v>866.65</v>
       </c>
       <c r="I15" s="26">
-        <v>223.38</v>
+        <v>901.18</v>
       </c>
       <c r="J15" s="26">
-        <v>215.69</v>
-      </c>
-      <c r="K15" s="26">
-        <v>228.89</v>
-      </c>
-      <c r="L15" s="27">
-        <v>3.2</v>
+        <v>849.3</v>
+      </c>
+      <c r="K15" s="26"/>
+      <c r="L15" s="26">
+        <v>0.47</v>
       </c>
       <c r="M15" s="17"/>
       <c r="N15" s="16" t="s">
         <v>108</v>
       </c>
       <c r="O15" s="18" t="s">
-        <v>132</v>
+        <v>32</v>
       </c>
       <c r="P15" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="Q15" s="31"/>
-      <c r="R15" s="28"/>
-      <c r="S15" s="28">
-        <v>7.72</v>
-      </c>
-      <c r="T15" s="28">
+      <c r="Q15" s="30"/>
+      <c r="R15" s="27"/>
+      <c r="S15" s="27">
+        <v>11.92</v>
+      </c>
+      <c r="T15" s="27">
         <f>IF(S15="","",SUM($S$5:S15))</f>
-        <v>16.61</v>
-      </c>
-      <c r="U15" s="28">
+        <v>12.64</v>
+      </c>
+      <c r="U15" s="27">
         <f>IF(T15="","",MAX(0,MAX($T$5:T15)))</f>
-        <v>17.809999999999999</v>
-      </c>
-      <c r="V15" s="28">
-        <f t="shared" si="0"/>
-        <v>-1.1999999999999993</v>
+        <v>12.64</v>
+      </c>
+      <c r="V15" s="27">
+        <f>IF(T15="","",T15-U15)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B16" s="24">
-        <v>46246.396024733796</v>
+        <v>46245.876891678243</v>
       </c>
       <c r="C16" s="24">
-        <v>46246.649064293983</v>
+        <v>46246.522651608801</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>145</v>
+        <v>37</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>129</v>
@@ -3659,60 +3660,60 @@
         <v>105</v>
       </c>
       <c r="H16" s="25">
-        <v>219.72</v>
+        <v>866.5</v>
       </c>
       <c r="I16" s="26">
-        <v>223.38</v>
+        <v>901.18</v>
       </c>
       <c r="J16" s="26">
-        <v>215.33</v>
+        <v>849.41</v>
       </c>
       <c r="K16" s="26">
-        <v>228.5</v>
-      </c>
-      <c r="L16" s="27">
-        <v>3.1</v>
+        <v>900.68</v>
+      </c>
+      <c r="L16" s="26">
+        <v>0.3</v>
       </c>
       <c r="M16" s="17"/>
       <c r="N16" s="16" t="s">
         <v>108</v>
       </c>
       <c r="O16" s="18" t="s">
-        <v>132</v>
+        <v>32</v>
       </c>
       <c r="P16" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="Q16" s="31"/>
-      <c r="R16" s="28"/>
-      <c r="S16" s="28">
-        <v>8.34</v>
-      </c>
-      <c r="T16" s="28">
+      <c r="Q16" s="30"/>
+      <c r="R16" s="27"/>
+      <c r="S16" s="27">
+        <v>7.64</v>
+      </c>
+      <c r="T16" s="27">
         <f>IF(S16="","",SUM($S$5:S16))</f>
-        <v>24.95</v>
-      </c>
-      <c r="U16" s="28">
+        <v>20.28</v>
+      </c>
+      <c r="U16" s="27">
         <f>IF(T16="","",MAX(0,MAX($T$5:T16)))</f>
-        <v>24.95</v>
-      </c>
-      <c r="V16" s="28">
-        <f t="shared" si="0"/>
+        <v>20.28</v>
+      </c>
+      <c r="V16" s="27">
+        <f>IF(T16="","",T16-U16)</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B17" s="24">
-        <v>46246.531361585643</v>
+        <v>46245.878077534726</v>
       </c>
       <c r="C17" s="24">
-        <v>46246.649064305559</v>
+        <v>46246.584874374996</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>129</v>
@@ -3724,60 +3725,60 @@
         <v>105</v>
       </c>
       <c r="H17" s="25">
-        <v>220.53</v>
+        <v>502.25</v>
       </c>
       <c r="I17" s="26">
-        <v>223.38</v>
+        <v>492.17</v>
       </c>
       <c r="J17" s="26">
-        <v>216.12</v>
+        <v>492.21</v>
       </c>
       <c r="K17" s="26">
-        <v>229.36</v>
-      </c>
-      <c r="L17" s="27">
-        <v>2</v>
+        <v>522.32000000000005</v>
+      </c>
+      <c r="L17" s="26">
+        <v>0.32</v>
       </c>
       <c r="M17" s="17"/>
       <c r="N17" s="16" t="s">
         <v>108</v>
       </c>
       <c r="O17" s="18" t="s">
-        <v>132</v>
+        <v>31</v>
       </c>
       <c r="P17" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="Q17" s="31"/>
-      <c r="R17" s="28"/>
-      <c r="S17" s="28">
-        <v>4.1900000000000004</v>
-      </c>
-      <c r="T17" s="28">
+      <c r="Q17" s="30"/>
+      <c r="R17" s="27"/>
+      <c r="S17" s="27">
+        <v>-2.4</v>
+      </c>
+      <c r="T17" s="27">
         <f>IF(S17="","",SUM($S$5:S17))</f>
-        <v>29.14</v>
-      </c>
-      <c r="U17" s="28">
+        <v>17.880000000000003</v>
+      </c>
+      <c r="U17" s="27">
         <f>IF(T17="","",MAX(0,MAX($T$5:T17)))</f>
-        <v>29.14</v>
-      </c>
-      <c r="V17" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20.28</v>
+      </c>
+      <c r="V17" s="27">
+        <f>IF(T17="","",T17-U17)</f>
+        <v>-2.3999999999999986</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B18" s="24">
-        <v>46246.573039317125</v>
+        <v>46246.396024733796</v>
       </c>
       <c r="C18" s="24">
-        <v>46246.649375057867</v>
+        <v>46246.649064293983</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>37</v>
+        <v>145</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>129</v>
@@ -3789,19 +3790,19 @@
         <v>105</v>
       </c>
       <c r="H18" s="25">
-        <v>916.5</v>
+        <v>219.72</v>
       </c>
       <c r="I18" s="26">
-        <v>923.88</v>
+        <v>223.38</v>
       </c>
       <c r="J18" s="26">
-        <v>898.09</v>
+        <v>215.33</v>
       </c>
       <c r="K18" s="26">
-        <v>953.32</v>
-      </c>
-      <c r="L18" s="27">
-        <v>0.65</v>
+        <v>228.5</v>
+      </c>
+      <c r="L18" s="26">
+        <v>3.1</v>
       </c>
       <c r="M18" s="17"/>
       <c r="N18" s="16" t="s">
@@ -3813,36 +3814,36 @@
       <c r="P18" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="Q18" s="31"/>
-      <c r="R18" s="28"/>
-      <c r="S18" s="28">
-        <v>3.53</v>
-      </c>
-      <c r="T18" s="28">
+      <c r="Q18" s="30"/>
+      <c r="R18" s="27"/>
+      <c r="S18" s="27">
+        <v>8.34</v>
+      </c>
+      <c r="T18" s="27">
         <f>IF(S18="","",SUM($S$5:S18))</f>
-        <v>32.67</v>
-      </c>
-      <c r="U18" s="28">
+        <v>26.220000000000002</v>
+      </c>
+      <c r="U18" s="27">
         <f>IF(T18="","",MAX(0,MAX($T$5:T18)))</f>
-        <v>32.67</v>
-      </c>
-      <c r="V18" s="28">
-        <f t="shared" si="0"/>
+        <v>26.220000000000002</v>
+      </c>
+      <c r="V18" s="27">
+        <f>IF(T18="","",T18-U18)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B19" s="24">
-        <v>46245.833421516203</v>
+        <v>46246.524338668984</v>
       </c>
       <c r="C19" s="24">
-        <v>46246.652417442128</v>
+        <v>46246.649064293983</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>129</v>
@@ -3854,17 +3855,19 @@
         <v>105</v>
       </c>
       <c r="H19" s="25">
-        <v>503.85</v>
+        <v>220.1</v>
       </c>
       <c r="I19" s="26">
-        <v>492.76</v>
+        <v>223.38</v>
       </c>
       <c r="J19" s="26">
-        <v>400</v>
-      </c>
-      <c r="K19" s="26"/>
-      <c r="L19" s="27">
-        <v>0.38</v>
+        <v>215.69</v>
+      </c>
+      <c r="K19" s="26">
+        <v>228.89</v>
+      </c>
+      <c r="L19" s="26">
+        <v>3.2</v>
       </c>
       <c r="M19" s="17"/>
       <c r="N19" s="16" t="s">
@@ -3876,36 +3879,36 @@
       <c r="P19" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="Q19" s="31"/>
-      <c r="R19" s="28"/>
-      <c r="S19" s="28">
-        <v>-3.14</v>
-      </c>
-      <c r="T19" s="28">
+      <c r="Q19" s="30"/>
+      <c r="R19" s="27"/>
+      <c r="S19" s="27">
+        <v>7.72</v>
+      </c>
+      <c r="T19" s="27">
         <f>IF(S19="","",SUM($S$5:S19))</f>
-        <v>29.53</v>
-      </c>
-      <c r="U19" s="28">
+        <v>33.940000000000005</v>
+      </c>
+      <c r="U19" s="27">
         <f>IF(T19="","",MAX(0,MAX($T$5:T19)))</f>
-        <v>32.67</v>
-      </c>
-      <c r="V19" s="28">
-        <f t="shared" si="0"/>
-        <v>-3.1400000000000006</v>
+        <v>33.940000000000005</v>
+      </c>
+      <c r="V19" s="27">
+        <f>IF(T19="","",T19-U19)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B20" s="24">
-        <v>46246.667747037034</v>
+        <v>46246.531361585643</v>
       </c>
       <c r="C20" s="24">
-        <v>46247.017419548611</v>
+        <v>46246.649064305559</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="E20" s="8" t="s">
         <v>129</v>
@@ -3917,180 +3920,182 @@
         <v>105</v>
       </c>
       <c r="H20" s="25">
-        <v>4424.96</v>
+        <v>220.53</v>
       </c>
       <c r="I20" s="26">
-        <v>4433.22</v>
-      </c>
-      <c r="J20" s="26"/>
+        <v>223.38</v>
+      </c>
+      <c r="J20" s="26">
+        <v>216.12</v>
+      </c>
       <c r="K20" s="26">
-        <v>4433.8100000000004</v>
-      </c>
-      <c r="L20" s="27">
-        <v>3.8</v>
+        <v>229.36</v>
+      </c>
+      <c r="L20" s="26">
+        <v>2</v>
       </c>
       <c r="M20" s="17"/>
       <c r="N20" s="16" t="s">
         <v>108</v>
       </c>
       <c r="O20" s="18" t="s">
-        <v>31</v>
+        <v>132</v>
       </c>
       <c r="P20" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="Q20" s="31"/>
-      <c r="R20" s="28"/>
-      <c r="S20" s="28">
-        <v>23.09</v>
-      </c>
-      <c r="T20" s="28">
+      <c r="Q20" s="30"/>
+      <c r="R20" s="27"/>
+      <c r="S20" s="27">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="T20" s="27">
         <f>IF(S20="","",SUM($S$5:S20))</f>
-        <v>52.620000000000005</v>
-      </c>
-      <c r="U20" s="28">
+        <v>38.130000000000003</v>
+      </c>
+      <c r="U20" s="27">
         <f>IF(T20="","",MAX(0,MAX($T$5:T20)))</f>
-        <v>52.620000000000005</v>
-      </c>
-      <c r="V20" s="28">
-        <f t="shared" si="0"/>
+        <v>38.130000000000003</v>
+      </c>
+      <c r="V20" s="27">
+        <f>IF(T20="","",T20-U20)</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="B21" s="24">
-        <v>46247.018141631939</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="B21" s="24"/>
       <c r="C21" s="24">
-        <v>46247.022170706019</v>
+        <v>46246.561113136573</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>107</v>
+        <v>37</v>
       </c>
       <c r="E21" s="8" t="s">
         <v>129</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G21" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="H21" s="25">
-        <v>4431.83</v>
-      </c>
+      <c r="H21" s="25"/>
       <c r="I21" s="26">
-        <v>4427.55</v>
+        <v>910.73</v>
       </c>
       <c r="J21" s="26"/>
-      <c r="K21" s="26"/>
-      <c r="L21" s="27">
-        <v>4.7</v>
+      <c r="K21" s="26">
+        <v>910</v>
+      </c>
+      <c r="L21" s="26">
+        <v>1.1499999999999999</v>
       </c>
       <c r="M21" s="17"/>
-      <c r="N21" s="16" t="s">
-        <v>108</v>
-      </c>
+      <c r="N21" s="16"/>
       <c r="O21" s="18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P21" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="Q21" s="31"/>
-      <c r="R21" s="28"/>
-      <c r="S21" s="28">
-        <v>14.8</v>
-      </c>
-      <c r="T21" s="28">
+      <c r="Q21" s="30"/>
+      <c r="R21" s="27"/>
+      <c r="S21" s="27">
+        <v>22.29</v>
+      </c>
+      <c r="T21" s="27">
         <f>IF(S21="","",SUM($S$5:S21))</f>
-        <v>67.42</v>
-      </c>
-      <c r="U21" s="28">
+        <v>60.42</v>
+      </c>
+      <c r="U21" s="27">
         <f>IF(T21="","",MAX(0,MAX($T$5:T21)))</f>
-        <v>67.42</v>
-      </c>
-      <c r="V21" s="28">
-        <f t="shared" si="0"/>
+        <v>60.42</v>
+      </c>
+      <c r="V21" s="27">
+        <f>IF(T21="","",T21-U21)</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="B22" s="24">
-        <v>46247.024765706017</v>
+        <v>46246.56257130787</v>
       </c>
       <c r="C22" s="24">
-        <v>46247.036773599539</v>
+        <v>46246.578073263889</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>107</v>
+        <v>150</v>
       </c>
       <c r="E22" s="8" t="s">
         <v>129</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G22" s="8" t="s">
         <v>105</v>
       </c>
       <c r="H22" s="25">
-        <v>4442.03</v>
+        <v>173.73</v>
       </c>
       <c r="I22" s="26">
-        <v>4431.0600000000004</v>
-      </c>
-      <c r="J22" s="26"/>
-      <c r="K22" s="26"/>
-      <c r="L22" s="27">
-        <v>4.9000000000000004</v>
+        <v>169.87</v>
+      </c>
+      <c r="J22" s="26">
+        <v>169.89</v>
+      </c>
+      <c r="K22" s="26">
+        <v>180.28</v>
+      </c>
+      <c r="L22" s="26">
+        <v>4</v>
       </c>
       <c r="M22" s="17"/>
       <c r="N22" s="16" t="s">
         <v>108</v>
       </c>
       <c r="O22" s="18" t="s">
-        <v>132</v>
+        <v>31</v>
       </c>
       <c r="P22" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="Q22" s="31"/>
-      <c r="R22" s="28"/>
-      <c r="S22" s="28">
-        <v>39.54</v>
-      </c>
-      <c r="T22" s="28">
+      <c r="Q22" s="30"/>
+      <c r="R22" s="27"/>
+      <c r="S22" s="27">
+        <v>-11.49</v>
+      </c>
+      <c r="T22" s="27">
         <f>IF(S22="","",SUM($S$5:S22))</f>
-        <v>106.96000000000001</v>
-      </c>
-      <c r="U22" s="28">
+        <v>48.93</v>
+      </c>
+      <c r="U22" s="27">
         <f>IF(T22="","",MAX(0,MAX($T$5:T22)))</f>
-        <v>106.96000000000001</v>
-      </c>
-      <c r="V22" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>60.42</v>
+      </c>
+      <c r="V22" s="27">
+        <f>IF(T22="","",T22-U22)</f>
+        <v>-11.490000000000002</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="B23" s="24">
-        <v>46247.343873298611</v>
+        <v>46246.573039317125</v>
       </c>
       <c r="C23" s="24">
-        <v>46247.348071689819</v>
+        <v>46246.649375057867</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>150</v>
+        <v>37</v>
       </c>
       <c r="E23" s="8" t="s">
         <v>129</v>
@@ -4102,60 +4107,60 @@
         <v>105</v>
       </c>
       <c r="H23" s="25">
-        <v>172.3</v>
+        <v>916.5</v>
       </c>
       <c r="I23" s="26">
-        <v>171.35</v>
+        <v>923.88</v>
       </c>
       <c r="J23" s="26">
-        <v>171.69</v>
+        <v>898.09</v>
       </c>
       <c r="K23" s="26">
-        <v>173.52</v>
-      </c>
-      <c r="L23" s="27">
-        <v>12.3</v>
+        <v>953.32</v>
+      </c>
+      <c r="L23" s="26">
+        <v>0.65</v>
       </c>
       <c r="M23" s="17"/>
       <c r="N23" s="16" t="s">
         <v>108</v>
       </c>
       <c r="O23" s="18" t="s">
-        <v>31</v>
+        <v>132</v>
       </c>
       <c r="P23" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="Q23" s="31"/>
-      <c r="R23" s="28"/>
-      <c r="S23" s="28">
-        <v>-8.73</v>
-      </c>
-      <c r="T23" s="28">
+      <c r="Q23" s="30"/>
+      <c r="R23" s="27"/>
+      <c r="S23" s="27">
+        <v>3.53</v>
+      </c>
+      <c r="T23" s="27">
         <f>IF(S23="","",SUM($S$5:S23))</f>
-        <v>98.23</v>
-      </c>
-      <c r="U23" s="28">
+        <v>52.46</v>
+      </c>
+      <c r="U23" s="27">
         <f>IF(T23="","",MAX(0,MAX($T$5:T23)))</f>
-        <v>106.96000000000001</v>
-      </c>
-      <c r="V23" s="28">
-        <f t="shared" si="0"/>
-        <v>-8.730000000000004</v>
+        <v>60.42</v>
+      </c>
+      <c r="V23" s="27">
+        <f>IF(T23="","",T23-U23)</f>
+        <v>-7.9600000000000009</v>
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B24" s="24">
-        <v>46247.413234340274</v>
+        <v>46246.667747037034</v>
       </c>
       <c r="C24" s="24">
-        <v>46247.460487893521</v>
+        <v>46247.017419548611</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>37</v>
+        <v>107</v>
       </c>
       <c r="E24" s="8" t="s">
         <v>129</v>
@@ -4167,84 +4172,78 @@
         <v>105</v>
       </c>
       <c r="H24" s="25">
-        <v>909.05</v>
+        <v>4424.96</v>
       </c>
       <c r="I24" s="26">
-        <v>913.66</v>
-      </c>
-      <c r="J24" s="26">
-        <v>905.22</v>
-      </c>
+        <v>4433.22</v>
+      </c>
+      <c r="J24" s="26"/>
       <c r="K24" s="26">
-        <v>913.6</v>
-      </c>
-      <c r="L24" s="27">
-        <v>2.31</v>
+        <v>4433.8100000000004</v>
+      </c>
+      <c r="L24" s="26">
+        <v>3.8</v>
       </c>
       <c r="M24" s="17"/>
       <c r="N24" s="16" t="s">
         <v>108</v>
       </c>
       <c r="O24" s="18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P24" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="Q24" s="31"/>
-      <c r="R24" s="28"/>
-      <c r="S24" s="28">
-        <v>7.84</v>
-      </c>
-      <c r="T24" s="28">
+      <c r="Q24" s="30"/>
+      <c r="R24" s="27"/>
+      <c r="S24" s="27">
+        <v>23.09</v>
+      </c>
+      <c r="T24" s="27">
         <f>IF(S24="","",SUM($S$5:S24))</f>
-        <v>106.07000000000001</v>
-      </c>
-      <c r="U24" s="28">
+        <v>75.55</v>
+      </c>
+      <c r="U24" s="27">
         <f>IF(T24="","",MAX(0,MAX($T$5:T24)))</f>
-        <v>106.96000000000001</v>
-      </c>
-      <c r="V24" s="28">
-        <f t="shared" si="0"/>
-        <v>-0.89000000000000057</v>
+        <v>75.55</v>
+      </c>
+      <c r="V24" s="27">
+        <f>IF(T24="","",T24-U24)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B25" s="24">
-        <v>46247.482705625</v>
+        <v>46247.018141631939</v>
       </c>
       <c r="C25" s="24">
-        <v>46247.483814699073</v>
+        <v>46247.022170706019</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>136</v>
+        <v>107</v>
       </c>
       <c r="E25" s="8" t="s">
         <v>129</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G25" s="8" t="s">
         <v>105</v>
       </c>
       <c r="H25" s="25">
-        <v>494.05</v>
+        <v>4431.83</v>
       </c>
       <c r="I25" s="26">
-        <v>492.95</v>
-      </c>
-      <c r="J25" s="26">
-        <v>493.07</v>
-      </c>
-      <c r="K25" s="26">
-        <v>495.38</v>
-      </c>
-      <c r="L25" s="27">
-        <v>4.25</v>
+        <v>4427.55</v>
+      </c>
+      <c r="J25" s="26"/>
+      <c r="K25" s="26"/>
+      <c r="L25" s="26">
+        <v>4.7</v>
       </c>
       <c r="M25" s="17"/>
       <c r="N25" s="16" t="s">
@@ -4256,36 +4255,36 @@
       <c r="P25" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="Q25" s="31"/>
-      <c r="R25" s="28"/>
-      <c r="S25" s="28">
-        <v>-3.49</v>
-      </c>
-      <c r="T25" s="28">
+      <c r="Q25" s="30"/>
+      <c r="R25" s="27"/>
+      <c r="S25" s="27">
+        <v>14.8</v>
+      </c>
+      <c r="T25" s="27">
         <f>IF(S25="","",SUM($S$5:S25))</f>
-        <v>102.58000000000001</v>
-      </c>
-      <c r="U25" s="28">
+        <v>90.35</v>
+      </c>
+      <c r="U25" s="27">
         <f>IF(T25="","",MAX(0,MAX($T$5:T25)))</f>
-        <v>106.96000000000001</v>
-      </c>
-      <c r="V25" s="28">
-        <f t="shared" si="0"/>
-        <v>-4.3799999999999955</v>
+        <v>90.35</v>
+      </c>
+      <c r="V25" s="27">
+        <f>IF(T25="","",T25-U25)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B26" s="24">
-        <v>46247.500309467592</v>
+        <v>46247.024765706017</v>
       </c>
       <c r="C26" s="24">
-        <v>46247.504149745371</v>
+        <v>46247.036773599539</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>150</v>
+        <v>107</v>
       </c>
       <c r="E26" s="8" t="s">
         <v>129</v>
@@ -4297,60 +4296,56 @@
         <v>105</v>
       </c>
       <c r="H26" s="25">
-        <v>170.8</v>
+        <v>4442.03</v>
       </c>
       <c r="I26" s="26">
-        <v>171.37</v>
-      </c>
-      <c r="J26" s="26">
-        <v>171.36</v>
-      </c>
-      <c r="K26" s="26">
-        <v>169.76</v>
-      </c>
-      <c r="L26" s="27">
-        <v>12.1</v>
+        <v>4431.0600000000004</v>
+      </c>
+      <c r="J26" s="26"/>
+      <c r="K26" s="26"/>
+      <c r="L26" s="26">
+        <v>4.9000000000000004</v>
       </c>
       <c r="M26" s="17"/>
       <c r="N26" s="16" t="s">
         <v>108</v>
       </c>
       <c r="O26" s="18" t="s">
-        <v>31</v>
+        <v>132</v>
       </c>
       <c r="P26" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="Q26" s="31"/>
-      <c r="R26" s="28"/>
-      <c r="S26" s="28">
-        <v>-5.15</v>
-      </c>
-      <c r="T26" s="28">
+      <c r="Q26" s="30"/>
+      <c r="R26" s="27"/>
+      <c r="S26" s="27">
+        <v>39.54</v>
+      </c>
+      <c r="T26" s="27">
         <f>IF(S26="","",SUM($S$5:S26))</f>
-        <v>97.43</v>
-      </c>
-      <c r="U26" s="28">
+        <v>129.88999999999999</v>
+      </c>
+      <c r="U26" s="27">
         <f>IF(T26="","",MAX(0,MAX($T$5:T26)))</f>
-        <v>106.96000000000001</v>
-      </c>
-      <c r="V26" s="28">
-        <f t="shared" si="0"/>
-        <v>-9.5300000000000011</v>
+        <v>129.88999999999999</v>
+      </c>
+      <c r="V26" s="27">
+        <f>IF(T26="","",T26-U26)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="B27" s="24">
-        <v>46247.468851817132</v>
+        <v>46247.343873298611</v>
       </c>
       <c r="C27" s="24">
-        <v>46247.51082314815</v>
+        <v>46247.348071689819</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>37</v>
+        <v>150</v>
       </c>
       <c r="E27" s="8" t="s">
         <v>129</v>
@@ -4362,19 +4357,19 @@
         <v>105</v>
       </c>
       <c r="H27" s="25">
-        <v>914.04</v>
+        <v>172.3</v>
       </c>
       <c r="I27" s="26">
-        <v>905.17</v>
+        <v>171.35</v>
       </c>
       <c r="J27" s="26">
-        <v>905.2</v>
+        <v>171.69</v>
       </c>
       <c r="K27" s="26">
-        <v>921.7</v>
-      </c>
-      <c r="L27" s="27">
-        <v>2.3199999999999998</v>
+        <v>173.52</v>
+      </c>
+      <c r="L27" s="26">
+        <v>12.3</v>
       </c>
       <c r="M27" s="17"/>
       <c r="N27" s="16" t="s">
@@ -4386,36 +4381,36 @@
       <c r="P27" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="Q27" s="31"/>
-      <c r="R27" s="28"/>
-      <c r="S27" s="28">
-        <v>-15.36</v>
-      </c>
-      <c r="T27" s="28">
+      <c r="Q27" s="30"/>
+      <c r="R27" s="27"/>
+      <c r="S27" s="27">
+        <v>-8.73</v>
+      </c>
+      <c r="T27" s="27">
         <f>IF(S27="","",SUM($S$5:S27))</f>
-        <v>82.070000000000007</v>
-      </c>
-      <c r="U27" s="28">
+        <v>121.15999999999998</v>
+      </c>
+      <c r="U27" s="27">
         <f>IF(T27="","",MAX(0,MAX($T$5:T27)))</f>
-        <v>106.96000000000001</v>
-      </c>
-      <c r="V27" s="28">
-        <f t="shared" si="0"/>
-        <v>-24.89</v>
+        <v>129.88999999999999</v>
+      </c>
+      <c r="V27" s="27">
+        <f>IF(T27="","",T27-U27)</f>
+        <v>-8.730000000000004</v>
       </c>
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="B28" s="24">
-        <v>46247.541936030088</v>
+        <v>46247.413234340274</v>
       </c>
       <c r="C28" s="24">
-        <v>46247.544830914354</v>
+        <v>46247.460487893521</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>145</v>
+        <v>37</v>
       </c>
       <c r="E28" s="8" t="s">
         <v>129</v>
@@ -4427,19 +4422,19 @@
         <v>105</v>
       </c>
       <c r="H28" s="25">
-        <v>224.11</v>
+        <v>909.05</v>
       </c>
       <c r="I28" s="26">
-        <v>224.55</v>
+        <v>913.66</v>
       </c>
       <c r="J28" s="26">
-        <v>223.31</v>
+        <v>905.22</v>
       </c>
       <c r="K28" s="26">
-        <v>224.54</v>
-      </c>
-      <c r="L28" s="27">
-        <v>9.1</v>
+        <v>913.6</v>
+      </c>
+      <c r="L28" s="26">
+        <v>2.31</v>
       </c>
       <c r="M28" s="17"/>
       <c r="N28" s="16" t="s">
@@ -4451,33 +4446,33 @@
       <c r="P28" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="Q28" s="31"/>
-      <c r="R28" s="28"/>
-      <c r="S28" s="28">
-        <v>2.94</v>
-      </c>
-      <c r="T28" s="28">
+      <c r="Q28" s="30"/>
+      <c r="R28" s="27"/>
+      <c r="S28" s="27">
+        <v>7.84</v>
+      </c>
+      <c r="T28" s="27">
         <f>IF(S28="","",SUM($S$5:S28))</f>
-        <v>85.01</v>
-      </c>
-      <c r="U28" s="28">
+        <v>128.99999999999997</v>
+      </c>
+      <c r="U28" s="27">
         <f>IF(T28="","",MAX(0,MAX($T$5:T28)))</f>
-        <v>106.96000000000001</v>
-      </c>
-      <c r="V28" s="28">
-        <f t="shared" si="0"/>
-        <v>-21.950000000000003</v>
+        <v>129.88999999999999</v>
+      </c>
+      <c r="V28" s="27">
+        <f>IF(T28="","",T28-U28)</f>
+        <v>-0.89000000000001478</v>
       </c>
     </row>
     <row r="29" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B29" s="24">
-        <v>46247.520945798606</v>
+        <v>46247.468851817132</v>
       </c>
       <c r="C29" s="24">
-        <v>46247.562861527782</v>
+        <v>46247.51082314815</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>37</v>
@@ -4492,60 +4487,60 @@
         <v>105</v>
       </c>
       <c r="H29" s="25">
-        <v>910.3</v>
+        <v>914.04</v>
       </c>
       <c r="I29" s="26">
-        <v>915.58</v>
+        <v>905.17</v>
       </c>
       <c r="J29" s="26">
-        <v>903.93</v>
+        <v>905.2</v>
       </c>
       <c r="K29" s="26">
-        <v>915.53</v>
-      </c>
-      <c r="L29" s="27">
-        <v>2.2599999999999998</v>
+        <v>921.7</v>
+      </c>
+      <c r="L29" s="26">
+        <v>2.3199999999999998</v>
       </c>
       <c r="M29" s="17"/>
       <c r="N29" s="16" t="s">
         <v>108</v>
       </c>
       <c r="O29" s="18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P29" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="Q29" s="31"/>
-      <c r="R29" s="28"/>
-      <c r="S29" s="28">
-        <v>8.7799999999999994</v>
-      </c>
-      <c r="T29" s="28">
+      <c r="Q29" s="30"/>
+      <c r="R29" s="27"/>
+      <c r="S29" s="27">
+        <v>-15.36</v>
+      </c>
+      <c r="T29" s="27">
         <f>IF(S29="","",SUM($S$5:S29))</f>
-        <v>93.79</v>
-      </c>
-      <c r="U29" s="28">
+        <v>113.63999999999997</v>
+      </c>
+      <c r="U29" s="27">
         <f>IF(T29="","",MAX(0,MAX($T$5:T29)))</f>
-        <v>106.96000000000001</v>
-      </c>
-      <c r="V29" s="28">
-        <f t="shared" si="0"/>
-        <v>-13.170000000000002</v>
+        <v>129.88999999999999</v>
+      </c>
+      <c r="V29" s="27">
+        <f>IF(T29="","",T29-U29)</f>
+        <v>-16.250000000000014</v>
       </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="B30" s="24">
-        <v>46247.552180451385</v>
+        <v>46247.482705625</v>
       </c>
       <c r="C30" s="24">
-        <v>46247.564742916671</v>
+        <v>46247.483814699073</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="E30" s="8" t="s">
         <v>129</v>
@@ -4557,84 +4552,84 @@
         <v>105</v>
       </c>
       <c r="H30" s="25">
-        <v>224.69</v>
+        <v>494.05</v>
       </c>
       <c r="I30" s="26">
-        <v>226.32</v>
+        <v>492.95</v>
       </c>
       <c r="J30" s="26">
-        <v>223.95</v>
+        <v>493.07</v>
       </c>
       <c r="K30" s="26">
-        <v>226.32</v>
-      </c>
-      <c r="L30" s="27">
-        <v>9.1999999999999993</v>
+        <v>495.38</v>
+      </c>
+      <c r="L30" s="26">
+        <v>4.25</v>
       </c>
       <c r="M30" s="17"/>
       <c r="N30" s="16" t="s">
         <v>108</v>
       </c>
       <c r="O30" s="18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P30" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="Q30" s="31"/>
-      <c r="R30" s="28"/>
-      <c r="S30" s="28">
-        <v>11.03</v>
-      </c>
-      <c r="T30" s="28">
+      <c r="Q30" s="30"/>
+      <c r="R30" s="27"/>
+      <c r="S30" s="27">
+        <v>-3.49</v>
+      </c>
+      <c r="T30" s="27">
         <f>IF(S30="","",SUM($S$5:S30))</f>
-        <v>104.82000000000001</v>
-      </c>
-      <c r="U30" s="28">
+        <v>110.14999999999998</v>
+      </c>
+      <c r="U30" s="27">
         <f>IF(T30="","",MAX(0,MAX($T$5:T30)))</f>
-        <v>106.96000000000001</v>
-      </c>
-      <c r="V30" s="28">
-        <f t="shared" si="0"/>
-        <v>-2.1400000000000006</v>
+        <v>129.88999999999999</v>
+      </c>
+      <c r="V30" s="27">
+        <f>IF(T30="","",T30-U30)</f>
+        <v>-19.740000000000009</v>
       </c>
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B31" s="24">
-        <v>46247.583357754629</v>
+        <v>46247.500309467592</v>
       </c>
       <c r="C31" s="24">
-        <v>46247.640776689819</v>
+        <v>46247.504149745371</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="E31" s="8" t="s">
         <v>129</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G31" s="8" t="s">
         <v>105</v>
       </c>
       <c r="H31" s="25">
-        <v>498.79</v>
+        <v>170.8</v>
       </c>
       <c r="I31" s="26">
-        <v>494.65</v>
+        <v>171.37</v>
       </c>
       <c r="J31" s="26">
-        <v>494.68</v>
+        <v>171.36</v>
       </c>
       <c r="K31" s="26">
-        <v>506.15</v>
-      </c>
-      <c r="L31" s="27">
-        <v>4.28</v>
+        <v>169.76</v>
+      </c>
+      <c r="L31" s="26">
+        <v>12.1</v>
       </c>
       <c r="M31" s="17"/>
       <c r="N31" s="16" t="s">
@@ -4646,36 +4641,36 @@
       <c r="P31" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="Q31" s="31"/>
-      <c r="R31" s="28"/>
-      <c r="S31" s="28">
-        <v>-13.22</v>
-      </c>
-      <c r="T31" s="28">
+      <c r="Q31" s="30"/>
+      <c r="R31" s="27"/>
+      <c r="S31" s="27">
+        <v>-5.15</v>
+      </c>
+      <c r="T31" s="27">
         <f>IF(S31="","",SUM($S$5:S31))</f>
-        <v>91.600000000000009</v>
-      </c>
-      <c r="U31" s="28">
+        <v>104.99999999999997</v>
+      </c>
+      <c r="U31" s="27">
         <f>IF(T31="","",MAX(0,MAX($T$5:T31)))</f>
-        <v>106.96000000000001</v>
-      </c>
-      <c r="V31" s="28">
-        <f t="shared" si="0"/>
-        <v>-15.36</v>
+        <v>129.88999999999999</v>
+      </c>
+      <c r="V31" s="27">
+        <f>IF(T31="","",T31-U31)</f>
+        <v>-24.890000000000015</v>
       </c>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B32" s="24">
-        <v>46247.566097199073</v>
+        <v>46247.520945798606</v>
       </c>
       <c r="C32" s="24">
-        <v>46247.642346562498</v>
+        <v>46247.562861527782</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>136</v>
+        <v>37</v>
       </c>
       <c r="E32" s="8" t="s">
         <v>129</v>
@@ -4687,84 +4682,84 @@
         <v>105</v>
       </c>
       <c r="H32" s="25">
-        <v>497.38</v>
+        <v>910.3</v>
       </c>
       <c r="I32" s="26">
-        <v>494.23</v>
+        <v>915.58</v>
       </c>
       <c r="J32" s="26">
-        <v>494.23</v>
+        <v>903.93</v>
       </c>
       <c r="K32" s="26">
-        <v>501.78</v>
-      </c>
-      <c r="L32" s="27">
-        <v>4.26</v>
+        <v>915.53</v>
+      </c>
+      <c r="L32" s="26">
+        <v>2.2599999999999998</v>
       </c>
       <c r="M32" s="17"/>
       <c r="N32" s="16" t="s">
         <v>108</v>
       </c>
       <c r="O32" s="18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P32" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="Q32" s="31"/>
-      <c r="R32" s="28"/>
-      <c r="S32" s="28">
-        <v>-10.01</v>
-      </c>
-      <c r="T32" s="28">
+      <c r="Q32" s="30"/>
+      <c r="R32" s="27"/>
+      <c r="S32" s="27">
+        <v>8.7799999999999994</v>
+      </c>
+      <c r="T32" s="27">
         <f>IF(S32="","",SUM($S$5:S32))</f>
-        <v>81.59</v>
-      </c>
-      <c r="U32" s="28">
+        <v>113.77999999999997</v>
+      </c>
+      <c r="U32" s="27">
         <f>IF(T32="","",MAX(0,MAX($T$5:T32)))</f>
-        <v>106.96000000000001</v>
-      </c>
-      <c r="V32" s="28">
-        <f t="shared" si="0"/>
-        <v>-25.370000000000005</v>
+        <v>129.88999999999999</v>
+      </c>
+      <c r="V32" s="27">
+        <f>IF(T32="","",T32-U32)</f>
+        <v>-16.110000000000014</v>
       </c>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="B33" s="24">
-        <v>46247.723664467594</v>
+        <v>46247.541936030088</v>
       </c>
       <c r="C33" s="24">
-        <v>46247.724871701386</v>
+        <v>46247.544830914354</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="E33" s="8" t="s">
         <v>129</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G33" s="8" t="s">
         <v>105</v>
       </c>
       <c r="H33" s="25">
-        <v>494.43</v>
+        <v>224.11</v>
       </c>
       <c r="I33" s="26">
-        <v>494.3</v>
+        <v>224.55</v>
       </c>
       <c r="J33" s="26">
-        <v>494.87</v>
+        <v>223.31</v>
       </c>
       <c r="K33" s="26">
-        <v>494.31</v>
-      </c>
-      <c r="L33" s="27">
-        <v>4.0999999999999996</v>
+        <v>224.54</v>
+      </c>
+      <c r="L33" s="26">
+        <v>9.1</v>
       </c>
       <c r="M33" s="17"/>
       <c r="N33" s="16" t="s">
@@ -4776,60 +4771,60 @@
       <c r="P33" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="Q33" s="31"/>
-      <c r="R33" s="28"/>
-      <c r="S33" s="28">
-        <v>0.39</v>
-      </c>
-      <c r="T33" s="28">
+      <c r="Q33" s="30"/>
+      <c r="R33" s="27"/>
+      <c r="S33" s="27">
+        <v>2.94</v>
+      </c>
+      <c r="T33" s="27">
         <f>IF(S33="","",SUM($S$5:S33))</f>
-        <v>81.98</v>
-      </c>
-      <c r="U33" s="28">
+        <v>116.71999999999997</v>
+      </c>
+      <c r="U33" s="27">
         <f>IF(T33="","",MAX(0,MAX($T$5:T33)))</f>
-        <v>106.96000000000001</v>
-      </c>
-      <c r="V33" s="28">
-        <f t="shared" si="0"/>
-        <v>-24.980000000000004</v>
+        <v>129.88999999999999</v>
+      </c>
+      <c r="V33" s="27">
+        <f>IF(T33="","",T33-U33)</f>
+        <v>-13.170000000000016</v>
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B34" s="24">
-        <v>46247.724332187499</v>
+        <v>46247.552180451385</v>
       </c>
       <c r="C34" s="24">
-        <v>46247.725060567129</v>
+        <v>46247.564742916671</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="E34" s="8" t="s">
         <v>129</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G34" s="8" t="s">
         <v>105</v>
       </c>
       <c r="H34" s="25">
-        <v>494.45</v>
+        <v>224.69</v>
       </c>
       <c r="I34" s="26">
-        <v>494.23</v>
+        <v>226.32</v>
       </c>
       <c r="J34" s="26">
-        <v>494.79</v>
+        <v>223.95</v>
       </c>
       <c r="K34" s="26">
-        <v>494.23</v>
-      </c>
-      <c r="L34" s="27">
-        <v>4.0999999999999996</v>
+        <v>226.32</v>
+      </c>
+      <c r="L34" s="26">
+        <v>9.1999999999999993</v>
       </c>
       <c r="M34" s="17"/>
       <c r="N34" s="16" t="s">
@@ -4841,33 +4836,33 @@
       <c r="P34" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="Q34" s="31"/>
-      <c r="R34" s="28"/>
-      <c r="S34" s="28">
-        <v>0.66</v>
-      </c>
-      <c r="T34" s="28">
+      <c r="Q34" s="30"/>
+      <c r="R34" s="27"/>
+      <c r="S34" s="27">
+        <v>11.03</v>
+      </c>
+      <c r="T34" s="27">
         <f>IF(S34="","",SUM($S$5:S34))</f>
-        <v>82.64</v>
-      </c>
-      <c r="U34" s="28">
+        <v>127.74999999999997</v>
+      </c>
+      <c r="U34" s="27">
         <f>IF(T34="","",MAX(0,MAX($T$5:T34)))</f>
-        <v>106.96000000000001</v>
-      </c>
-      <c r="V34" s="28">
-        <f t="shared" si="0"/>
-        <v>-24.320000000000007</v>
+        <v>129.88999999999999</v>
+      </c>
+      <c r="V34" s="27">
+        <f>IF(T34="","",T34-U34)</f>
+        <v>-2.1400000000000148</v>
       </c>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B35" s="24">
-        <v>46247.725067847219</v>
+        <v>46247.566097199073</v>
       </c>
       <c r="C35" s="24">
-        <v>46247.727486365737</v>
+        <v>46247.642346562498</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>136</v>
@@ -4876,25 +4871,25 @@
         <v>129</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G35" s="8" t="s">
         <v>105</v>
       </c>
       <c r="H35" s="25">
-        <v>494.02</v>
+        <v>497.38</v>
       </c>
       <c r="I35" s="26">
-        <v>494.51</v>
+        <v>494.23</v>
       </c>
       <c r="J35" s="26">
-        <v>494.47</v>
+        <v>494.23</v>
       </c>
       <c r="K35" s="26">
-        <v>493.84</v>
-      </c>
-      <c r="L35" s="27">
-        <v>4.08</v>
+        <v>501.78</v>
+      </c>
+      <c r="L35" s="26">
+        <v>4.26</v>
       </c>
       <c r="M35" s="17"/>
       <c r="N35" s="16" t="s">
@@ -4906,33 +4901,33 @@
       <c r="P35" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="Q35" s="31"/>
-      <c r="R35" s="28"/>
-      <c r="S35" s="28">
-        <v>-1.49</v>
-      </c>
-      <c r="T35" s="28">
+      <c r="Q35" s="30"/>
+      <c r="R35" s="27"/>
+      <c r="S35" s="27">
+        <v>-10.01</v>
+      </c>
+      <c r="T35" s="27">
         <f>IF(S35="","",SUM($S$5:S35))</f>
-        <v>81.150000000000006</v>
-      </c>
-      <c r="U35" s="28">
+        <v>117.73999999999997</v>
+      </c>
+      <c r="U35" s="27">
         <f>IF(T35="","",MAX(0,MAX($T$5:T35)))</f>
-        <v>106.96000000000001</v>
-      </c>
-      <c r="V35" s="28">
-        <f t="shared" si="0"/>
-        <v>-25.810000000000002</v>
+        <v>129.88999999999999</v>
+      </c>
+      <c r="V35" s="27">
+        <f>IF(T35="","",T35-U35)</f>
+        <v>-12.15000000000002</v>
       </c>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="B36" s="24">
-        <v>46247.728506597225</v>
+        <v>46247.583357754629</v>
       </c>
       <c r="C36" s="24">
-        <v>46247.731019710649</v>
+        <v>46247.640776689819</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>136</v>
@@ -4941,63 +4936,63 @@
         <v>129</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G36" s="8" t="s">
         <v>105</v>
       </c>
       <c r="H36" s="25">
-        <v>494.34</v>
+        <v>498.79</v>
       </c>
       <c r="I36" s="26">
-        <v>494.35</v>
+        <v>494.65</v>
       </c>
       <c r="J36" s="26">
-        <v>494.65</v>
+        <v>494.68</v>
       </c>
       <c r="K36" s="26">
-        <v>494.04</v>
-      </c>
-      <c r="L36" s="27">
-        <v>4.09</v>
+        <v>506.15</v>
+      </c>
+      <c r="L36" s="26">
+        <v>4.28</v>
       </c>
       <c r="M36" s="17"/>
       <c r="N36" s="16" t="s">
         <v>108</v>
       </c>
       <c r="O36" s="18" t="s">
-        <v>132</v>
+        <v>31</v>
       </c>
       <c r="P36" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="Q36" s="31"/>
-      <c r="R36" s="28"/>
-      <c r="S36" s="28">
-        <v>-0.03</v>
-      </c>
-      <c r="T36" s="28">
+      <c r="Q36" s="30"/>
+      <c r="R36" s="27"/>
+      <c r="S36" s="27">
+        <v>-13.22</v>
+      </c>
+      <c r="T36" s="27">
         <f>IF(S36="","",SUM($S$5:S36))</f>
-        <v>81.12</v>
-      </c>
-      <c r="U36" s="28">
+        <v>104.51999999999997</v>
+      </c>
+      <c r="U36" s="27">
         <f>IF(T36="","",MAX(0,MAX($T$5:T36)))</f>
-        <v>106.96000000000001</v>
-      </c>
-      <c r="V36" s="28">
-        <f t="shared" si="0"/>
-        <v>-25.840000000000003</v>
+        <v>129.88999999999999</v>
+      </c>
+      <c r="V36" s="27">
+        <f>IF(T36="","",T36-U36)</f>
+        <v>-25.370000000000019</v>
       </c>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B37" s="24">
-        <v>46247.730572349537</v>
+        <v>46247.664698587963</v>
       </c>
       <c r="C37" s="24">
-        <v>46247.731019710649</v>
+        <v>46247.765913402778</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>136</v>
@@ -5006,25 +5001,21 @@
         <v>129</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G37" s="8" t="s">
         <v>105</v>
       </c>
       <c r="H37" s="25">
-        <v>494.3</v>
+        <v>495.17</v>
       </c>
       <c r="I37" s="26">
-        <v>494.35</v>
-      </c>
-      <c r="J37" s="26">
-        <v>494.63</v>
-      </c>
-      <c r="K37" s="26">
-        <v>494.07</v>
-      </c>
-      <c r="L37" s="27">
-        <v>4.08</v>
+        <v>493.63</v>
+      </c>
+      <c r="J37" s="26"/>
+      <c r="K37" s="26"/>
+      <c r="L37" s="26">
+        <v>11</v>
       </c>
       <c r="M37" s="17"/>
       <c r="N37" s="16" t="s">
@@ -5036,33 +5027,33 @@
       <c r="P37" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="Q37" s="31"/>
-      <c r="R37" s="28"/>
-      <c r="S37" s="28">
-        <v>-0.15</v>
-      </c>
-      <c r="T37" s="28">
+      <c r="Q37" s="30"/>
+      <c r="R37" s="27"/>
+      <c r="S37" s="27">
+        <v>-12.65</v>
+      </c>
+      <c r="T37" s="27">
         <f>IF(S37="","",SUM($S$5:S37))</f>
-        <v>80.97</v>
-      </c>
-      <c r="U37" s="28">
+        <v>91.869999999999962</v>
+      </c>
+      <c r="U37" s="27">
         <f>IF(T37="","",MAX(0,MAX($T$5:T37)))</f>
-        <v>106.96000000000001</v>
-      </c>
-      <c r="V37" s="28">
-        <f t="shared" si="0"/>
-        <v>-25.990000000000009</v>
+        <v>129.88999999999999</v>
+      </c>
+      <c r="V37" s="27">
+        <f>IF(T37="","",T37-U37)</f>
+        <v>-38.020000000000024</v>
       </c>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B38" s="24">
-        <v>46247.664698587963</v>
+        <v>46247.723664467594</v>
       </c>
       <c r="C38" s="24">
-        <v>46247.765913402778</v>
+        <v>46247.724871701386</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>136</v>
@@ -5071,62 +5062,66 @@
         <v>129</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G38" s="8" t="s">
         <v>105</v>
       </c>
       <c r="H38" s="25">
-        <v>495.17</v>
+        <v>494.43</v>
       </c>
       <c r="I38" s="26">
-        <v>493.63</v>
-      </c>
-      <c r="J38" s="26"/>
-      <c r="K38" s="26"/>
-      <c r="L38" s="27">
-        <v>11</v>
+        <v>494.3</v>
+      </c>
+      <c r="J38" s="26">
+        <v>494.87</v>
+      </c>
+      <c r="K38" s="26">
+        <v>494.31</v>
+      </c>
+      <c r="L38" s="26">
+        <v>4.0999999999999996</v>
       </c>
       <c r="M38" s="17"/>
       <c r="N38" s="16" t="s">
         <v>108</v>
       </c>
       <c r="O38" s="18" t="s">
-        <v>132</v>
+        <v>32</v>
       </c>
       <c r="P38" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="Q38" s="31"/>
-      <c r="R38" s="28"/>
-      <c r="S38" s="28">
-        <v>-12.65</v>
-      </c>
-      <c r="T38" s="28">
+      <c r="Q38" s="30"/>
+      <c r="R38" s="27"/>
+      <c r="S38" s="27">
+        <v>0.39</v>
+      </c>
+      <c r="T38" s="27">
         <f>IF(S38="","",SUM($S$5:S38))</f>
-        <v>68.319999999999993</v>
-      </c>
-      <c r="U38" s="28">
+        <v>92.259999999999962</v>
+      </c>
+      <c r="U38" s="27">
         <f>IF(T38="","",MAX(0,MAX($T$5:T38)))</f>
-        <v>106.96000000000001</v>
-      </c>
-      <c r="V38" s="28">
-        <f t="shared" si="0"/>
-        <v>-38.640000000000015</v>
+        <v>129.88999999999999</v>
+      </c>
+      <c r="V38" s="27">
+        <f>IF(T38="","",T38-U38)</f>
+        <v>-37.630000000000024</v>
       </c>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="B39" s="24">
-        <v>46247.766599282404</v>
+        <v>46247.724332187499</v>
       </c>
       <c r="C39" s="24">
-        <v>46247.829866631946</v>
+        <v>46247.725060567129</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>37</v>
+        <v>136</v>
       </c>
       <c r="E39" s="8" t="s">
         <v>129</v>
@@ -5138,19 +5133,23 @@
         <v>105</v>
       </c>
       <c r="H39" s="25">
-        <v>966.55</v>
+        <v>494.45</v>
       </c>
       <c r="I39" s="26">
-        <v>949.62</v>
-      </c>
-      <c r="J39" s="26"/>
-      <c r="K39" s="26"/>
-      <c r="L39" s="27">
-        <v>4</v>
+        <v>494.23</v>
+      </c>
+      <c r="J39" s="26">
+        <v>494.79</v>
+      </c>
+      <c r="K39" s="26">
+        <v>494.23</v>
+      </c>
+      <c r="L39" s="26">
+        <v>4.0999999999999996</v>
       </c>
       <c r="M39" s="17"/>
       <c r="N39" s="16" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="O39" s="18" t="s">
         <v>32</v>
@@ -5158,220 +5157,228 @@
       <c r="P39" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="Q39" s="31"/>
-      <c r="R39" s="28"/>
-      <c r="S39" s="28">
-        <v>49.86</v>
-      </c>
-      <c r="T39" s="28">
+      <c r="Q39" s="30"/>
+      <c r="R39" s="27"/>
+      <c r="S39" s="27">
+        <v>0.66</v>
+      </c>
+      <c r="T39" s="27">
         <f>IF(S39="","",SUM($S$5:S39))</f>
-        <v>118.17999999999999</v>
-      </c>
-      <c r="U39" s="28">
+        <v>92.919999999999959</v>
+      </c>
+      <c r="U39" s="27">
         <f>IF(T39="","",MAX(0,MAX($T$5:T39)))</f>
-        <v>118.17999999999999</v>
-      </c>
-      <c r="V39" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>129.88999999999999</v>
+      </c>
+      <c r="V39" s="27">
+        <f>IF(T39="","",T39-U39)</f>
+        <v>-36.970000000000027</v>
       </c>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="B40" s="24">
-        <v>46247.843897175924</v>
+        <v>46247.725067847219</v>
       </c>
       <c r="C40" s="24">
-        <v>46247.908600138893</v>
+        <v>46247.727486365737</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>37</v>
+        <v>136</v>
       </c>
       <c r="E40" s="8" t="s">
         <v>129</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G40" s="8" t="s">
         <v>105</v>
       </c>
       <c r="H40" s="25">
-        <v>957.33</v>
+        <v>494.02</v>
       </c>
       <c r="I40" s="26">
-        <v>961.14</v>
+        <v>494.51</v>
       </c>
       <c r="J40" s="26">
-        <v>950.29</v>
+        <v>494.47</v>
       </c>
       <c r="K40" s="26">
-        <v>966.86</v>
-      </c>
-      <c r="L40" s="27">
-        <v>2.25</v>
+        <v>493.84</v>
+      </c>
+      <c r="L40" s="26">
+        <v>4.08</v>
       </c>
       <c r="M40" s="17"/>
       <c r="N40" s="16" t="s">
         <v>108</v>
       </c>
       <c r="O40" s="18" t="s">
-        <v>132</v>
+        <v>31</v>
       </c>
       <c r="P40" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="Q40" s="31"/>
-      <c r="R40" s="28"/>
-      <c r="S40" s="28">
-        <v>6.31</v>
-      </c>
-      <c r="T40" s="28">
+      <c r="Q40" s="30"/>
+      <c r="R40" s="27"/>
+      <c r="S40" s="27">
+        <v>-1.49</v>
+      </c>
+      <c r="T40" s="27">
         <f>IF(S40="","",SUM($S$5:S40))</f>
-        <v>124.49</v>
-      </c>
-      <c r="U40" s="28">
+        <v>91.429999999999964</v>
+      </c>
+      <c r="U40" s="27">
         <f>IF(T40="","",MAX(0,MAX($T$5:T40)))</f>
-        <v>124.49</v>
-      </c>
-      <c r="V40" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>129.88999999999999</v>
+      </c>
+      <c r="V40" s="27">
+        <f>IF(T40="","",T40-U40)</f>
+        <v>-38.460000000000022</v>
       </c>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>198</v>
+        <v>137</v>
       </c>
       <c r="B41" s="24">
-        <v>46247.943435185181</v>
+        <v>46247.728506597225</v>
       </c>
       <c r="C41" s="24">
-        <v>46247.944994791666</v>
+        <v>46247.731019710649</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="E41" s="8" t="s">
         <v>129</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G41" s="8" t="s">
         <v>105</v>
       </c>
       <c r="H41" s="25">
-        <v>4360.9799999999996</v>
+        <v>494.34</v>
       </c>
       <c r="I41" s="26">
-        <v>4361.51</v>
-      </c>
-      <c r="J41" s="26"/>
-      <c r="K41" s="26"/>
-      <c r="L41" s="27">
-        <v>4.5</v>
+        <v>494.35</v>
+      </c>
+      <c r="J41" s="26">
+        <v>494.65</v>
+      </c>
+      <c r="K41" s="26">
+        <v>494.04</v>
+      </c>
+      <c r="L41" s="26">
+        <v>4.09</v>
       </c>
       <c r="M41" s="17"/>
-      <c r="N41" s="16"/>
+      <c r="N41" s="16" t="s">
+        <v>108</v>
+      </c>
       <c r="O41" s="18" t="s">
-        <v>31</v>
+        <v>132</v>
       </c>
       <c r="P41" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="Q41" s="31"/>
-      <c r="R41" s="28"/>
-      <c r="S41" s="28">
-        <v>1.76</v>
-      </c>
-      <c r="T41" s="28">
+      <c r="Q41" s="30"/>
+      <c r="R41" s="27"/>
+      <c r="S41" s="27">
+        <v>-0.03</v>
+      </c>
+      <c r="T41" s="27">
         <f>IF(S41="","",SUM($S$5:S41))</f>
-        <v>126.25</v>
-      </c>
-      <c r="U41" s="28">
+        <v>91.399999999999963</v>
+      </c>
+      <c r="U41" s="27">
         <f>IF(T41="","",MAX(0,MAX($T$5:T41)))</f>
-        <v>126.25</v>
-      </c>
-      <c r="V41" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>129.88999999999999</v>
+      </c>
+      <c r="V41" s="27">
+        <f>IF(T41="","",T41-U41)</f>
+        <v>-38.490000000000023</v>
       </c>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>197</v>
+        <v>138</v>
       </c>
       <c r="B42" s="24">
-        <v>46247.968786597223</v>
+        <v>46247.730572349537</v>
       </c>
       <c r="C42" s="24">
-        <v>46247.98143299768</v>
+        <v>46247.731019710649</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>37</v>
+        <v>136</v>
       </c>
       <c r="E42" s="8" t="s">
         <v>129</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G42" s="8" t="s">
         <v>105</v>
       </c>
       <c r="H42" s="25">
-        <v>964.05</v>
+        <v>494.3</v>
       </c>
       <c r="I42" s="26">
-        <v>961.25</v>
+        <v>494.35</v>
       </c>
       <c r="J42" s="26">
-        <v>961.47</v>
+        <v>494.63</v>
       </c>
       <c r="K42" s="26">
-        <v>967.37</v>
-      </c>
-      <c r="L42" s="27">
-        <v>2.19</v>
+        <v>494.07</v>
+      </c>
+      <c r="L42" s="26">
+        <v>4.08</v>
       </c>
       <c r="M42" s="17"/>
-      <c r="N42" s="16"/>
+      <c r="N42" s="16" t="s">
+        <v>108</v>
+      </c>
       <c r="O42" s="18" t="s">
-        <v>31</v>
+        <v>132</v>
       </c>
       <c r="P42" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="Q42" s="31"/>
-      <c r="R42" s="28"/>
-      <c r="S42" s="28">
-        <v>-4.58</v>
-      </c>
-      <c r="T42" s="28">
+      <c r="Q42" s="30"/>
+      <c r="R42" s="27"/>
+      <c r="S42" s="27">
+        <v>-0.15</v>
+      </c>
+      <c r="T42" s="27">
         <f>IF(S42="","",SUM($S$5:S42))</f>
-        <v>121.67</v>
-      </c>
-      <c r="U42" s="28">
+        <v>91.249999999999957</v>
+      </c>
+      <c r="U42" s="27">
         <f>IF(T42="","",MAX(0,MAX($T$5:T42)))</f>
-        <v>126.25</v>
-      </c>
-      <c r="V42" s="28">
-        <f t="shared" si="0"/>
-        <v>-4.5799999999999983</v>
+        <v>129.88999999999999</v>
+      </c>
+      <c r="V42" s="27">
+        <f>IF(T42="","",T42-U42)</f>
+        <v>-38.640000000000029</v>
       </c>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>196</v>
+        <v>134</v>
       </c>
       <c r="B43" s="24">
-        <v>46248.340323124998</v>
+        <v>46247.766599282404</v>
       </c>
       <c r="C43" s="24">
-        <v>46248.346137337961</v>
+        <v>46247.829866631946</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>37</v>
@@ -5380,61 +5387,59 @@
         <v>129</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G43" s="8" t="s">
         <v>105</v>
       </c>
       <c r="H43" s="25">
-        <v>967.46</v>
+        <v>966.55</v>
       </c>
       <c r="I43" s="26">
-        <v>962.05</v>
-      </c>
-      <c r="J43" s="26">
-        <v>962.3</v>
-      </c>
-      <c r="K43" s="26">
-        <v>972.98</v>
-      </c>
-      <c r="L43" s="27">
-        <v>2.12</v>
+        <v>949.62</v>
+      </c>
+      <c r="J43" s="26"/>
+      <c r="K43" s="26"/>
+      <c r="L43" s="26">
+        <v>4</v>
       </c>
       <c r="M43" s="17"/>
-      <c r="N43" s="16"/>
+      <c r="N43" s="16" t="s">
+        <v>106</v>
+      </c>
       <c r="O43" s="18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P43" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="Q43" s="31"/>
-      <c r="R43" s="28"/>
-      <c r="S43" s="28">
-        <v>-8.5399999999999991</v>
-      </c>
-      <c r="T43" s="28">
+      <c r="Q43" s="30"/>
+      <c r="R43" s="27"/>
+      <c r="S43" s="27">
+        <v>49.86</v>
+      </c>
+      <c r="T43" s="27">
         <f>IF(S43="","",SUM($S$5:S43))</f>
-        <v>113.13</v>
-      </c>
-      <c r="U43" s="28">
+        <v>141.10999999999996</v>
+      </c>
+      <c r="U43" s="27">
         <f>IF(T43="","",MAX(0,MAX($T$5:T43)))</f>
-        <v>126.25</v>
-      </c>
-      <c r="V43" s="28">
-        <f t="shared" si="0"/>
-        <v>-13.120000000000005</v>
+        <v>141.10999999999996</v>
+      </c>
+      <c r="V43" s="27">
+        <f>IF(T43="","",T43-U43)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>195</v>
+        <v>131</v>
       </c>
       <c r="B44" s="24">
-        <v>46247.968784351848</v>
+        <v>46247.843897175924</v>
       </c>
       <c r="C44" s="24">
-        <v>46248.410362337963</v>
+        <v>46247.908600138893</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>37</v>
@@ -5449,58 +5454,60 @@
         <v>105</v>
       </c>
       <c r="H44" s="25">
-        <v>964.05</v>
+        <v>957.33</v>
       </c>
       <c r="I44" s="26">
-        <v>970.7</v>
+        <v>961.14</v>
       </c>
       <c r="J44" s="26">
-        <v>957.64</v>
+        <v>950.29</v>
       </c>
       <c r="K44" s="26">
-        <v>970.65</v>
-      </c>
-      <c r="L44" s="27">
-        <v>2.19</v>
+        <v>966.86</v>
+      </c>
+      <c r="L44" s="26">
+        <v>2.25</v>
       </c>
       <c r="M44" s="17"/>
-      <c r="N44" s="16"/>
+      <c r="N44" s="16" t="s">
+        <v>108</v>
+      </c>
       <c r="O44" s="18" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="P44" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="Q44" s="31"/>
-      <c r="R44" s="28"/>
-      <c r="S44" s="28">
-        <v>10.69</v>
-      </c>
-      <c r="T44" s="28">
+      <c r="Q44" s="30"/>
+      <c r="R44" s="27"/>
+      <c r="S44" s="27">
+        <v>6.31</v>
+      </c>
+      <c r="T44" s="27">
         <f>IF(S44="","",SUM($S$5:S44))</f>
-        <v>123.82</v>
-      </c>
-      <c r="U44" s="28">
+        <v>147.41999999999996</v>
+      </c>
+      <c r="U44" s="27">
         <f>IF(T44="","",MAX(0,MAX($T$5:T44)))</f>
-        <v>126.25</v>
-      </c>
-      <c r="V44" s="28">
-        <f t="shared" si="0"/>
-        <v>-2.4300000000000068</v>
+        <v>147.41999999999996</v>
+      </c>
+      <c r="V44" s="27">
+        <f>IF(T44="","",T44-U44)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B45" s="24">
-        <v>46248.54184017361</v>
+        <v>46247.943435185181</v>
       </c>
       <c r="C45" s="24">
-        <v>46248.554862696757</v>
+        <v>46247.944994791666</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>37</v>
+        <v>107</v>
       </c>
       <c r="E45" s="8" t="s">
         <v>129</v>
@@ -5512,19 +5519,15 @@
         <v>105</v>
       </c>
       <c r="H45" s="25">
-        <v>981.52</v>
+        <v>4360.9799999999996</v>
       </c>
       <c r="I45" s="26">
-        <v>976.6</v>
-      </c>
-      <c r="J45" s="26">
-        <v>976.72</v>
-      </c>
-      <c r="K45" s="26">
-        <v>987.74</v>
-      </c>
-      <c r="L45" s="27">
-        <v>1.78</v>
+        <v>4361.51</v>
+      </c>
+      <c r="J45" s="26"/>
+      <c r="K45" s="26"/>
+      <c r="L45" s="26">
+        <v>4.5</v>
       </c>
       <c r="M45" s="17"/>
       <c r="N45" s="16"/>
@@ -5534,33 +5537,33 @@
       <c r="P45" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="Q45" s="31"/>
-      <c r="R45" s="28"/>
-      <c r="S45" s="28">
-        <v>-6.51</v>
-      </c>
-      <c r="T45" s="28">
+      <c r="Q45" s="30"/>
+      <c r="R45" s="27"/>
+      <c r="S45" s="27">
+        <v>1.76</v>
+      </c>
+      <c r="T45" s="27">
         <f>IF(S45="","",SUM($S$5:S45))</f>
-        <v>117.30999999999999</v>
-      </c>
-      <c r="U45" s="28">
+        <v>149.17999999999995</v>
+      </c>
+      <c r="U45" s="27">
         <f>IF(T45="","",MAX(0,MAX($T$5:T45)))</f>
-        <v>126.25</v>
-      </c>
-      <c r="V45" s="28">
-        <f t="shared" si="0"/>
-        <v>-8.9400000000000119</v>
+        <v>149.17999999999995</v>
+      </c>
+      <c r="V45" s="27">
+        <f>IF(T45="","",T45-U45)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B46" s="24">
-        <v>46248.458362870369</v>
+        <v>46247.945559097221</v>
       </c>
       <c r="C46" s="24">
-        <v>46248.563556724534</v>
+        <v>46248.688509097221</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>37</v>
@@ -5569,61 +5572,59 @@
         <v>129</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G46" s="8" t="s">
         <v>105</v>
       </c>
       <c r="H46" s="25">
-        <v>978.05</v>
+        <v>961.65</v>
       </c>
       <c r="I46" s="26">
-        <v>964.21</v>
-      </c>
-      <c r="J46" s="26">
-        <v>964.34</v>
-      </c>
+        <v>963.02</v>
+      </c>
+      <c r="J46" s="26"/>
       <c r="K46" s="26">
-        <v>993.92</v>
-      </c>
-      <c r="L46" s="27">
-        <v>1.86</v>
+        <v>950</v>
+      </c>
+      <c r="L46" s="26">
+        <v>6</v>
       </c>
       <c r="M46" s="17"/>
       <c r="N46" s="16"/>
       <c r="O46" s="18" t="s">
-        <v>31</v>
+        <v>132</v>
       </c>
       <c r="P46" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="Q46" s="31"/>
-      <c r="R46" s="28"/>
-      <c r="S46" s="28">
-        <v>-19.14</v>
-      </c>
-      <c r="T46" s="28">
+      <c r="Q46" s="30"/>
+      <c r="R46" s="27"/>
+      <c r="S46" s="27">
+        <v>-6.11</v>
+      </c>
+      <c r="T46" s="27">
         <f>IF(S46="","",SUM($S$5:S46))</f>
-        <v>98.169999999999987</v>
-      </c>
-      <c r="U46" s="28">
+        <v>143.06999999999994</v>
+      </c>
+      <c r="U46" s="27">
         <f>IF(T46="","",MAX(0,MAX($T$5:T46)))</f>
-        <v>126.25</v>
-      </c>
-      <c r="V46" s="28">
-        <f t="shared" si="0"/>
-        <v>-28.080000000000013</v>
+        <v>149.17999999999995</v>
+      </c>
+      <c r="V46" s="27">
+        <f>IF(T46="","",T46-U46)</f>
+        <v>-6.1100000000000136</v>
       </c>
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B47" s="24">
-        <v>46248.573065763892</v>
+        <v>46247.968784351848</v>
       </c>
       <c r="C47" s="24">
-        <v>46248.659597280093</v>
+        <v>46248.410362337963</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>37</v>
@@ -5638,55 +5639,55 @@
         <v>105</v>
       </c>
       <c r="H47" s="25">
-        <v>972.03</v>
+        <v>964.05</v>
       </c>
       <c r="I47" s="26">
-        <v>957.33</v>
+        <v>970.7</v>
       </c>
       <c r="J47" s="26">
-        <v>957.35</v>
+        <v>957.64</v>
       </c>
       <c r="K47" s="26">
-        <v>990.08</v>
-      </c>
-      <c r="L47" s="27">
-        <v>1.94</v>
+        <v>970.65</v>
+      </c>
+      <c r="L47" s="26">
+        <v>2.19</v>
       </c>
       <c r="M47" s="17"/>
       <c r="N47" s="16"/>
       <c r="O47" s="18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P47" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="Q47" s="31"/>
-      <c r="R47" s="28"/>
-      <c r="S47" s="28">
-        <v>-21.18</v>
-      </c>
-      <c r="T47" s="28">
+      <c r="Q47" s="30"/>
+      <c r="R47" s="27"/>
+      <c r="S47" s="27">
+        <v>10.69</v>
+      </c>
+      <c r="T47" s="27">
         <f>IF(S47="","",SUM($S$5:S47))</f>
-        <v>76.989999999999981</v>
-      </c>
-      <c r="U47" s="28">
+        <v>153.75999999999993</v>
+      </c>
+      <c r="U47" s="27">
         <f>IF(T47="","",MAX(0,MAX($T$5:T47)))</f>
-        <v>126.25</v>
-      </c>
-      <c r="V47" s="28">
-        <f t="shared" si="0"/>
-        <v>-49.260000000000019</v>
+        <v>153.75999999999993</v>
+      </c>
+      <c r="V47" s="27">
+        <f>IF(T47="","",T47-U47)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="B48" s="24">
-        <v>46247.945559097221</v>
+        <v>46247.968786597223</v>
       </c>
       <c r="C48" s="24">
-        <v>46248.688509097221</v>
+        <v>46247.98143299768</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>37</v>
@@ -5695,82 +5696,88 @@
         <v>129</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G48" s="8" t="s">
         <v>105</v>
       </c>
       <c r="H48" s="25">
-        <v>961.65</v>
+        <v>964.05</v>
       </c>
       <c r="I48" s="26">
-        <v>963.02</v>
-      </c>
-      <c r="J48" s="26"/>
+        <v>961.25</v>
+      </c>
+      <c r="J48" s="26">
+        <v>961.47</v>
+      </c>
       <c r="K48" s="26">
-        <v>950</v>
-      </c>
-      <c r="L48" s="27">
-        <v>6</v>
+        <v>967.37</v>
+      </c>
+      <c r="L48" s="26">
+        <v>2.19</v>
       </c>
       <c r="M48" s="17"/>
       <c r="N48" s="16"/>
       <c r="O48" s="18" t="s">
-        <v>132</v>
+        <v>31</v>
       </c>
       <c r="P48" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="Q48" s="31"/>
-      <c r="R48" s="28"/>
-      <c r="S48" s="28">
-        <v>-6.11</v>
-      </c>
-      <c r="T48" s="28">
+      <c r="Q48" s="30"/>
+      <c r="R48" s="27"/>
+      <c r="S48" s="27">
+        <v>-4.58</v>
+      </c>
+      <c r="T48" s="27">
         <f>IF(S48="","",SUM($S$5:S48))</f>
-        <v>70.879999999999981</v>
-      </c>
-      <c r="U48" s="28">
+        <v>149.17999999999992</v>
+      </c>
+      <c r="U48" s="27">
         <f>IF(T48="","",MAX(0,MAX($T$5:T48)))</f>
-        <v>126.25</v>
-      </c>
-      <c r="V48" s="28">
-        <f t="shared" si="0"/>
-        <v>-55.370000000000019</v>
+        <v>153.75999999999993</v>
+      </c>
+      <c r="V48" s="27">
+        <f>IF(T48="","",T48-U48)</f>
+        <v>-4.5800000000000125</v>
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="B49" s="24">
-        <v>46248.688867638892</v>
+        <v>46248.340323124998</v>
       </c>
       <c r="C49" s="24">
-        <v>46248.689919548611</v>
+        <v>46248.346137337961</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>107</v>
+        <v>37</v>
       </c>
       <c r="E49" s="8" t="s">
         <v>129</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G49" s="8" t="s">
         <v>105</v>
       </c>
       <c r="H49" s="25">
-        <v>4384.6899999999996</v>
+        <v>967.46</v>
       </c>
       <c r="I49" s="26">
-        <v>4381.72</v>
-      </c>
-      <c r="J49" s="26"/>
-      <c r="K49" s="26"/>
-      <c r="L49" s="27">
-        <v>5</v>
+        <v>962.05</v>
+      </c>
+      <c r="J49" s="26">
+        <v>962.3</v>
+      </c>
+      <c r="K49" s="26">
+        <v>972.98</v>
+      </c>
+      <c r="L49" s="26">
+        <v>2.12</v>
       </c>
       <c r="M49" s="17"/>
       <c r="N49" s="16"/>
@@ -5780,33 +5787,33 @@
       <c r="P49" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="Q49" s="31"/>
-      <c r="R49" s="28"/>
-      <c r="S49" s="28">
-        <v>10.88</v>
-      </c>
-      <c r="T49" s="28">
+      <c r="Q49" s="30"/>
+      <c r="R49" s="27"/>
+      <c r="S49" s="27">
+        <v>-8.5399999999999991</v>
+      </c>
+      <c r="T49" s="27">
         <f>IF(S49="","",SUM($S$5:S49))</f>
-        <v>81.759999999999977</v>
-      </c>
-      <c r="U49" s="28">
+        <v>140.63999999999993</v>
+      </c>
+      <c r="U49" s="27">
         <f>IF(T49="","",MAX(0,MAX($T$5:T49)))</f>
-        <v>126.25</v>
-      </c>
-      <c r="V49" s="28">
-        <f t="shared" si="0"/>
-        <v>-44.490000000000023</v>
+        <v>153.75999999999993</v>
+      </c>
+      <c r="V49" s="27">
+        <f>IF(T49="","",T49-U49)</f>
+        <v>-13.120000000000005</v>
       </c>
     </row>
     <row r="50" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B50" s="24">
-        <v>46248.691412094908</v>
+        <v>46248.458362870369</v>
       </c>
       <c r="C50" s="24">
-        <v>46248.694326273151</v>
+        <v>46248.563556724534</v>
       </c>
       <c r="D50" s="5" t="s">
         <v>37</v>
@@ -5821,15 +5828,19 @@
         <v>105</v>
       </c>
       <c r="H50" s="25">
-        <v>964.04</v>
+        <v>978.05</v>
       </c>
       <c r="I50" s="26">
-        <v>965.23</v>
-      </c>
-      <c r="J50" s="26"/>
-      <c r="K50" s="26"/>
-      <c r="L50" s="27">
-        <v>5.7</v>
+        <v>964.21</v>
+      </c>
+      <c r="J50" s="26">
+        <v>964.34</v>
+      </c>
+      <c r="K50" s="26">
+        <v>993.92</v>
+      </c>
+      <c r="L50" s="26">
+        <v>1.86</v>
       </c>
       <c r="M50" s="17"/>
       <c r="N50" s="16"/>
@@ -5839,95 +5850,99 @@
       <c r="P50" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="Q50" s="31"/>
-      <c r="R50" s="28"/>
-      <c r="S50" s="28">
-        <v>4.97</v>
-      </c>
-      <c r="T50" s="28">
+      <c r="Q50" s="30"/>
+      <c r="R50" s="27"/>
+      <c r="S50" s="27">
+        <v>-19.14</v>
+      </c>
+      <c r="T50" s="27">
         <f>IF(S50="","",SUM($S$5:S50))</f>
-        <v>86.729999999999976</v>
-      </c>
-      <c r="U50" s="28">
+        <v>121.49999999999993</v>
+      </c>
+      <c r="U50" s="27">
         <f>IF(T50="","",MAX(0,MAX($T$5:T50)))</f>
-        <v>126.25</v>
-      </c>
-      <c r="V50" s="28">
-        <f t="shared" si="0"/>
-        <v>-39.520000000000024</v>
+        <v>153.75999999999993</v>
+      </c>
+      <c r="V50" s="27">
+        <f>IF(T50="","",T50-U50)</f>
+        <v>-32.260000000000005</v>
       </c>
     </row>
     <row r="51" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B51" s="24">
-        <v>46248.694526527775</v>
+        <v>46248.54184017361</v>
       </c>
       <c r="C51" s="24">
-        <v>46248.710030624999</v>
+        <v>46248.554862696757</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>107</v>
+        <v>37</v>
       </c>
       <c r="E51" s="8" t="s">
         <v>129</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G51" s="8" t="s">
         <v>105</v>
       </c>
       <c r="H51" s="25">
-        <v>4388.3500000000004</v>
+        <v>981.52</v>
       </c>
       <c r="I51" s="26">
-        <v>4383.3100000000004</v>
-      </c>
-      <c r="J51" s="26"/>
-      <c r="K51" s="26"/>
-      <c r="L51" s="27">
-        <v>5.0999999999999996</v>
+        <v>976.6</v>
+      </c>
+      <c r="J51" s="26">
+        <v>976.72</v>
+      </c>
+      <c r="K51" s="26">
+        <v>987.74</v>
+      </c>
+      <c r="L51" s="26">
+        <v>1.78</v>
       </c>
       <c r="M51" s="17"/>
       <c r="N51" s="16"/>
       <c r="O51" s="18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P51" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="Q51" s="31"/>
-      <c r="R51" s="28"/>
-      <c r="S51" s="28">
-        <v>18.850000000000001</v>
-      </c>
-      <c r="T51" s="28">
+      <c r="Q51" s="30"/>
+      <c r="R51" s="27"/>
+      <c r="S51" s="27">
+        <v>-6.51</v>
+      </c>
+      <c r="T51" s="27">
         <f>IF(S51="","",SUM($S$5:S51))</f>
-        <v>105.57999999999998</v>
-      </c>
-      <c r="U51" s="28">
+        <v>114.98999999999992</v>
+      </c>
+      <c r="U51" s="27">
         <f>IF(T51="","",MAX(0,MAX($T$5:T51)))</f>
-        <v>126.25</v>
-      </c>
-      <c r="V51" s="28">
-        <f t="shared" si="0"/>
-        <v>-20.670000000000016</v>
+        <v>153.75999999999993</v>
+      </c>
+      <c r="V51" s="27">
+        <f>IF(T51="","",T51-U51)</f>
+        <v>-38.77000000000001</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B52" s="24">
-        <v>46248.748028136572</v>
+        <v>46248.573065763892</v>
       </c>
       <c r="C52" s="24">
-        <v>46248.754242465278</v>
+        <v>46248.659597280093</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>107</v>
+        <v>37</v>
       </c>
       <c r="E52" s="8" t="s">
         <v>129</v>
@@ -5939,15 +5954,19 @@
         <v>105</v>
       </c>
       <c r="H52" s="25">
-        <v>4377.62</v>
+        <v>972.03</v>
       </c>
       <c r="I52" s="26">
-        <v>4381.05</v>
-      </c>
-      <c r="J52" s="26"/>
-      <c r="K52" s="26"/>
-      <c r="L52" s="27">
-        <v>5.2</v>
+        <v>957.33</v>
+      </c>
+      <c r="J52" s="26">
+        <v>957.35</v>
+      </c>
+      <c r="K52" s="26">
+        <v>990.08</v>
+      </c>
+      <c r="L52" s="26">
+        <v>1.94</v>
       </c>
       <c r="M52" s="17"/>
       <c r="N52" s="16"/>
@@ -5957,56 +5976,56 @@
       <c r="P52" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="Q52" s="31"/>
-      <c r="R52" s="28"/>
-      <c r="S52" s="28">
-        <v>13.09</v>
-      </c>
-      <c r="T52" s="28">
+      <c r="Q52" s="30"/>
+      <c r="R52" s="27"/>
+      <c r="S52" s="27">
+        <v>-21.18</v>
+      </c>
+      <c r="T52" s="27">
         <f>IF(S52="","",SUM($S$5:S52))</f>
-        <v>118.66999999999999</v>
-      </c>
-      <c r="U52" s="28">
+        <v>93.809999999999917</v>
+      </c>
+      <c r="U52" s="27">
         <f>IF(T52="","",MAX(0,MAX($T$5:T52)))</f>
-        <v>126.25</v>
-      </c>
-      <c r="V52" s="28">
-        <f t="shared" si="0"/>
-        <v>-7.5800000000000125</v>
+        <v>153.75999999999993</v>
+      </c>
+      <c r="V52" s="27">
+        <f>IF(T52="","",T52-U52)</f>
+        <v>-59.950000000000017</v>
       </c>
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B53" s="24">
-        <v>46248.763731203704</v>
+        <v>46248.688867638892</v>
       </c>
       <c r="C53" s="24">
-        <v>46248.79132856481</v>
+        <v>46248.689919548611</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>37</v>
+        <v>107</v>
       </c>
       <c r="E53" s="8" t="s">
         <v>129</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G53" s="8" t="s">
         <v>105</v>
       </c>
       <c r="H53" s="25">
-        <v>962.92</v>
+        <v>4384.6899999999996</v>
       </c>
       <c r="I53" s="26">
-        <v>964.35</v>
+        <v>4381.72</v>
       </c>
       <c r="J53" s="26"/>
       <c r="K53" s="26"/>
-      <c r="L53" s="27">
-        <v>6</v>
+      <c r="L53" s="26">
+        <v>5</v>
       </c>
       <c r="M53" s="17"/>
       <c r="N53" s="16"/>
@@ -6016,73 +6035,633 @@
       <c r="P53" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="Q53" s="31"/>
-      <c r="R53" s="28"/>
-      <c r="S53" s="28">
+      <c r="Q53" s="30"/>
+      <c r="R53" s="27"/>
+      <c r="S53" s="27">
+        <v>10.88</v>
+      </c>
+      <c r="T53" s="27">
+        <f>IF(S53="","",SUM($S$5:S53))</f>
+        <v>104.68999999999991</v>
+      </c>
+      <c r="U53" s="27">
+        <f>IF(T53="","",MAX(0,MAX($T$5:T53)))</f>
+        <v>153.75999999999993</v>
+      </c>
+      <c r="V53" s="27">
+        <f>IF(T53="","",T53-U53)</f>
+        <v>-49.070000000000022</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="B54" s="24">
+        <v>46248.691412094908</v>
+      </c>
+      <c r="C54" s="24">
+        <v>46248.694326273151</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="G54" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="H54" s="25">
+        <v>964.04</v>
+      </c>
+      <c r="I54" s="26">
+        <v>965.23</v>
+      </c>
+      <c r="J54" s="26"/>
+      <c r="K54" s="26"/>
+      <c r="L54" s="26">
+        <v>5.7</v>
+      </c>
+      <c r="M54" s="17"/>
+      <c r="N54" s="16"/>
+      <c r="O54" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="P54" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q54" s="30"/>
+      <c r="R54" s="27"/>
+      <c r="S54" s="27">
+        <v>4.97</v>
+      </c>
+      <c r="T54" s="27">
+        <f>IF(S54="","",SUM($S$5:S54))</f>
+        <v>109.65999999999991</v>
+      </c>
+      <c r="U54" s="27">
+        <f>IF(T54="","",MAX(0,MAX($T$5:T54)))</f>
+        <v>153.75999999999993</v>
+      </c>
+      <c r="V54" s="27">
+        <f>IF(T54="","",T54-U54)</f>
+        <v>-44.100000000000023</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="B55" s="24">
+        <v>46248.694526527775</v>
+      </c>
+      <c r="C55" s="24">
+        <v>46248.710030624999</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G55" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="H55" s="25">
+        <v>4388.3500000000004</v>
+      </c>
+      <c r="I55" s="26">
+        <v>4383.3100000000004</v>
+      </c>
+      <c r="J55" s="26"/>
+      <c r="K55" s="26"/>
+      <c r="L55" s="26">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="M55" s="17"/>
+      <c r="N55" s="16"/>
+      <c r="O55" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="P55" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q55" s="30"/>
+      <c r="R55" s="27"/>
+      <c r="S55" s="27">
+        <v>18.850000000000001</v>
+      </c>
+      <c r="T55" s="27">
+        <f>IF(S55="","",SUM($S$5:S55))</f>
+        <v>128.50999999999991</v>
+      </c>
+      <c r="U55" s="27">
+        <f>IF(T55="","",MAX(0,MAX($T$5:T55)))</f>
+        <v>153.75999999999993</v>
+      </c>
+      <c r="V55" s="27">
+        <f>IF(T55="","",T55-U55)</f>
+        <v>-25.250000000000028</v>
+      </c>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="B56" s="24">
+        <v>46248.748028136572</v>
+      </c>
+      <c r="C56" s="24">
+        <v>46248.754242465278</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="H56" s="25">
+        <v>4377.62</v>
+      </c>
+      <c r="I56" s="26">
+        <v>4381.05</v>
+      </c>
+      <c r="J56" s="26"/>
+      <c r="K56" s="26"/>
+      <c r="L56" s="26">
+        <v>5.2</v>
+      </c>
+      <c r="M56" s="17"/>
+      <c r="N56" s="16"/>
+      <c r="O56" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="P56" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q56" s="30"/>
+      <c r="R56" s="27"/>
+      <c r="S56" s="27">
+        <v>13.09</v>
+      </c>
+      <c r="T56" s="27">
+        <f>IF(S56="","",SUM($S$5:S56))</f>
+        <v>141.59999999999991</v>
+      </c>
+      <c r="U56" s="27">
+        <f>IF(T56="","",MAX(0,MAX($T$5:T56)))</f>
+        <v>153.75999999999993</v>
+      </c>
+      <c r="V56" s="27">
+        <f>IF(T56="","",T56-U56)</f>
+        <v>-12.160000000000025</v>
+      </c>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="B57" s="24">
+        <v>46248.763731203704</v>
+      </c>
+      <c r="C57" s="24">
+        <v>46248.79132856481</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="G57" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="H57" s="25">
+        <v>962.92</v>
+      </c>
+      <c r="I57" s="26">
+        <v>964.35</v>
+      </c>
+      <c r="J57" s="26"/>
+      <c r="K57" s="26"/>
+      <c r="L57" s="26">
+        <v>6</v>
+      </c>
+      <c r="M57" s="17"/>
+      <c r="N57" s="16"/>
+      <c r="O57" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="P57" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q57" s="30"/>
+      <c r="R57" s="27"/>
+      <c r="S57" s="27">
         <v>6.3</v>
       </c>
-      <c r="T53" s="28">
-        <f>IF(S53="","",SUM($S$5:S53))</f>
-        <v>124.96999999999998</v>
-      </c>
-      <c r="U53" s="28">
-        <f>IF(T53="","",MAX(0,MAX($T$5:T53)))</f>
-        <v>126.25</v>
-      </c>
-      <c r="V53" s="28">
-        <f t="shared" si="0"/>
-        <v>-1.2800000000000153</v>
-      </c>
-    </row>
-    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="I54" s="4"/>
-      <c r="J54" s="4"/>
-      <c r="K54" s="4"/>
-    </row>
-    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="I55" s="4"/>
-      <c r="J55" s="4"/>
-      <c r="K55" s="4"/>
-    </row>
-    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="I56" s="4"/>
-      <c r="J56" s="4"/>
-      <c r="K56" s="4"/>
-    </row>
-    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="I57" s="4"/>
-      <c r="J57" s="4"/>
-      <c r="K57" s="4"/>
+      <c r="T57" s="27">
+        <f>IF(S57="","",SUM($S$5:S57))</f>
+        <v>147.89999999999992</v>
+      </c>
+      <c r="U57" s="27">
+        <f>IF(T57="","",MAX(0,MAX($T$5:T57)))</f>
+        <v>153.75999999999993</v>
+      </c>
+      <c r="V57" s="27">
+        <f>IF(T57="","",T57-U57)</f>
+        <v>-5.8600000000000136</v>
+      </c>
     </row>
     <row r="58" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="I58" s="4"/>
-      <c r="J58" s="4"/>
-      <c r="K58" s="4"/>
+      <c r="A58" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="B58" s="24">
+        <v>46251.70142297454</v>
+      </c>
+      <c r="C58" s="24">
+        <v>46251.712206284719</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G58" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="H58" s="25">
+        <v>226.99</v>
+      </c>
+      <c r="I58" s="26">
+        <v>226.77</v>
+      </c>
+      <c r="J58" s="26">
+        <v>227.23</v>
+      </c>
+      <c r="K58" s="26">
+        <v>226.77</v>
+      </c>
+      <c r="L58" s="26">
+        <v>8.4</v>
+      </c>
+      <c r="M58" s="17"/>
+      <c r="N58" s="16"/>
+      <c r="O58" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="P58" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q58" s="30"/>
+      <c r="R58" s="27"/>
+      <c r="S58" s="27">
+        <v>1.35</v>
+      </c>
+      <c r="T58" s="27">
+        <f>IF(S58="","",SUM($S$5:S58))</f>
+        <v>149.24999999999991</v>
+      </c>
+      <c r="U58" s="27">
+        <f>IF(T58="","",MAX(0,MAX($T$5:T58)))</f>
+        <v>153.75999999999993</v>
+      </c>
+      <c r="V58" s="27">
+        <f>IF(T58="","",T58-U58)</f>
+        <v>-4.5100000000000193</v>
+      </c>
     </row>
     <row r="59" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="I59" s="4"/>
-      <c r="J59" s="4"/>
-      <c r="K59" s="4"/>
+      <c r="A59" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="B59" s="24">
+        <v>46251.709573761575</v>
+      </c>
+      <c r="C59" s="24">
+        <v>46251.718889965283</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G59" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="H59" s="25">
+        <v>1031.8900000000001</v>
+      </c>
+      <c r="I59" s="26">
+        <v>1026.49</v>
+      </c>
+      <c r="J59" s="26"/>
+      <c r="K59" s="26">
+        <v>1029.82</v>
+      </c>
+      <c r="L59" s="26">
+        <v>1.5</v>
+      </c>
+      <c r="M59" s="17"/>
+      <c r="N59" s="16"/>
+      <c r="O59" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="P59" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q59" s="30"/>
+      <c r="R59" s="27"/>
+      <c r="S59" s="27">
+        <v>5.93</v>
+      </c>
+      <c r="T59" s="27">
+        <f>IF(S59="","",SUM($S$5:S59))</f>
+        <v>155.17999999999992</v>
+      </c>
+      <c r="U59" s="27">
+        <f>IF(T59="","",MAX(0,MAX($T$5:T59)))</f>
+        <v>155.17999999999992</v>
+      </c>
+      <c r="V59" s="27">
+        <f>IF(T59="","",T59-U59)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="60" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="I60" s="4"/>
-      <c r="J60" s="4"/>
-      <c r="K60" s="4"/>
+      <c r="A60" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="B60" s="24">
+        <v>46251.730867268518</v>
+      </c>
+      <c r="C60" s="24">
+        <v>46251.76232065972</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="G60" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="H60" s="25">
+        <v>479.19</v>
+      </c>
+      <c r="I60" s="26">
+        <v>479.32</v>
+      </c>
+      <c r="J60" s="26"/>
+      <c r="K60" s="26">
+        <v>480.14</v>
+      </c>
+      <c r="L60" s="26">
+        <v>5</v>
+      </c>
+      <c r="M60" s="17"/>
+      <c r="N60" s="16"/>
+      <c r="O60" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="P60" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q60" s="30"/>
+      <c r="R60" s="27"/>
+      <c r="S60" s="27">
+        <v>0.48</v>
+      </c>
+      <c r="T60" s="27">
+        <f>IF(S60="","",SUM($S$5:S60))</f>
+        <v>155.65999999999991</v>
+      </c>
+      <c r="U60" s="27">
+        <f>IF(T60="","",MAX(0,MAX($T$5:T60)))</f>
+        <v>155.65999999999991</v>
+      </c>
+      <c r="V60" s="27">
+        <f>IF(T60="","",T60-U60)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="61" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="I61" s="4"/>
-      <c r="J61" s="4"/>
-      <c r="K61" s="4"/>
+      <c r="A61" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="B61" s="24">
+        <v>46251.773695081021</v>
+      </c>
+      <c r="C61" s="24">
+        <v>46251.774025879626</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E61" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G61" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="H61" s="25">
+        <v>479.32</v>
+      </c>
+      <c r="I61" s="26">
+        <v>479.57</v>
+      </c>
+      <c r="J61" s="26">
+        <v>479.87</v>
+      </c>
+      <c r="K61" s="26">
+        <v>478.72</v>
+      </c>
+      <c r="L61" s="26">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="M61" s="17"/>
+      <c r="N61" s="16"/>
+      <c r="O61" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="P61" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q61" s="30"/>
+      <c r="R61" s="27"/>
+      <c r="S61" s="27">
+        <v>-0.75</v>
+      </c>
+      <c r="T61" s="27">
+        <f>IF(S61="","",SUM($S$5:S61))</f>
+        <v>154.90999999999991</v>
+      </c>
+      <c r="U61" s="27">
+        <f>IF(T61="","",MAX(0,MAX($T$5:T61)))</f>
+        <v>155.65999999999991</v>
+      </c>
+      <c r="V61" s="27">
+        <f>IF(T61="","",T61-U61)</f>
+        <v>-0.75</v>
+      </c>
     </row>
     <row r="62" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="I62" s="4"/>
-      <c r="J62" s="4"/>
-      <c r="K62" s="4"/>
+      <c r="A62" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="B62" s="24">
+        <v>46251.777838819442</v>
+      </c>
+      <c r="C62" s="24">
+        <v>46251.778358703705</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="F62" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G62" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="H62" s="25">
+        <v>479.3</v>
+      </c>
+      <c r="I62" s="26">
+        <v>479.59</v>
+      </c>
+      <c r="J62" s="26">
+        <v>479.93</v>
+      </c>
+      <c r="K62" s="26">
+        <v>478.76</v>
+      </c>
+      <c r="L62" s="26">
+        <v>4.01</v>
+      </c>
+      <c r="M62" s="17"/>
+      <c r="N62" s="16"/>
+      <c r="O62" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="P62" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q62" s="30"/>
+      <c r="R62" s="27"/>
+      <c r="S62" s="27">
+        <v>-0.86</v>
+      </c>
+      <c r="T62" s="27">
+        <f>IF(S62="","",SUM($S$5:S62))</f>
+        <v>154.0499999999999</v>
+      </c>
+      <c r="U62" s="27">
+        <f>IF(T62="","",MAX(0,MAX($T$5:T62)))</f>
+        <v>155.65999999999991</v>
+      </c>
+      <c r="V62" s="27">
+        <f>IF(T62="","",T62-U62)</f>
+        <v>-1.6100000000000136</v>
+      </c>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="I63" s="4"/>
-      <c r="J63" s="4"/>
-      <c r="K63" s="4"/>
+      <c r="A63" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="B63" s="24">
+        <v>46251.783350428246</v>
+      </c>
+      <c r="C63" s="24">
+        <v>46251.784032453703</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="G63" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="H63" s="25">
+        <v>480.32</v>
+      </c>
+      <c r="I63" s="26">
+        <v>480.01</v>
+      </c>
+      <c r="J63" s="26">
+        <v>479.76</v>
+      </c>
+      <c r="K63" s="26">
+        <v>480.93</v>
+      </c>
+      <c r="L63" s="26">
+        <v>4</v>
+      </c>
+      <c r="M63" s="17"/>
+      <c r="N63" s="16"/>
+      <c r="O63" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="P63" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q63" s="30"/>
+      <c r="R63" s="27"/>
+      <c r="S63" s="27">
+        <v>-0.92</v>
+      </c>
+      <c r="T63" s="27">
+        <f>IF(S63="","",SUM($S$5:S63))</f>
+        <v>153.12999999999991</v>
+      </c>
+      <c r="U63" s="27">
+        <f>IF(T63="","",MAX(0,MAX($T$5:T63)))</f>
+        <v>155.65999999999991</v>
+      </c>
+      <c r="V63" s="27">
+        <f>IF(T63="","",T63-U63)</f>
+        <v>-2.5300000000000011</v>
+      </c>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.25">
       <c r="I64" s="4"/>
@@ -8383,11 +8962,6 @@
       <c r="I523" s="4"/>
       <c r="J523" s="4"/>
       <c r="K523" s="4"/>
-    </row>
-    <row r="524" spans="9:11" x14ac:dyDescent="0.25">
-      <c r="I524" s="4"/>
-      <c r="J524" s="4"/>
-      <c r="K524" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -8395,31 +8969,31 @@
     <mergeCell ref="A1:V1"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
-  <conditionalFormatting sqref="O5:O53 L8:L9 L35:L524">
-    <cfRule type="cellIs" dxfId="15" priority="1" operator="greaterThan">
+  <conditionalFormatting sqref="L8:L9 O5:O63 L35:L523">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K5:K53 J35:J524 N5:N53" xr:uid="{C60695FE-46C3-4171-82E8-5C0A8593648E}">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5:D53" xr:uid="{F8748047-6E27-4C5D-9DCB-D8B9CBB6B0A9}">
-      <formula1>"Trading 212,Capital"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5:C524 F5:F53" xr:uid="{E63373C3-00C1-448B-87D9-D6C6EF541310}">
-      <formula1>"BUY,SELL"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J5:J34" xr:uid="{21A667BE-7F78-4E55-AADF-25C7FA095C89}">
       <formula1>"Hedging,Strategy,Gut Feeling,Trending"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M5:M53" xr:uid="{21AE8715-933C-47DF-A9FC-2EE4397A2351}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N5:N63 J35:J523 K5:K63" xr:uid="{C60695FE-46C3-4171-82E8-5C0A8593648E}">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5:D63" xr:uid="{F8748047-6E27-4C5D-9DCB-D8B9CBB6B0A9}">
+      <formula1>"Trading 212,Capital"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F63 C5:C523" xr:uid="{E63373C3-00C1-448B-87D9-D6C6EF541310}">
+      <formula1>"BUY,SELL"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M5:M63" xr:uid="{21AE8715-933C-47DF-A9FC-2EE4397A2351}">
       <formula1>"Manual,Autotrader"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G5:G53" xr:uid="{923C59D8-53A9-4DC2-A21F-0806AEC42E86}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G5:G63" xr:uid="{923C59D8-53A9-4DC2-A21F-0806AEC42E86}">
       <formula1>"Capital,Trading 212"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8442,24 +9016,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="31" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
@@ -8479,11 +9053,11 @@
       <c r="C4" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D4" s="43" t="s">
+      <c r="D4" s="48" t="s">
         <v>102</v>
       </c>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
     </row>
     <row r="5" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
@@ -8491,17 +9065,17 @@
       </c>
       <c r="B5" s="10">
         <f>IFERROR(COUNTIF(TradeLog[Outcome (P/L)],"&gt;0")/COUNT(TradeLog[Outcome (P/L)]),0)</f>
-        <v>0.51020408163265307</v>
+        <v>0.52542372881355937</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D5" s="44" t="str">
+      <c r="D5" s="42" t="str">
         <f>COUNT(TradeLog[Outcome (P/L)])&amp;" closed Capital trades have generated "&amp;TEXT(B11,"£#,##0.00;[Red]-£#,##0.00")&amp;" in total P/L. The win rate is "&amp;TEXT(B5,"0.0%")&amp;", while the average win of "&amp;TEXT(B6,"£#,##0.00")&amp;" is "&amp;TEXT(IFERROR(ABS(B6/B7),0),"0.0x")&amp;" the average loss. Expectancy remains "&amp;TEXT(B8,"£#,##0.00;[Red]-£#,##0.00")&amp;" per trade, with a maximum drawdown of "&amp;TEXT(B10,"£#,##0.00;[Red]-£#,##0.00")&amp;"."</f>
-        <v>49 closed Capital trades have generated £124.97 in total P/L. The win rate is 51.0%, while the average win of £11.20 is 1.7x the average loss. Expectancy remains £2.55 per trade, with a maximum drawdown of -£55.37.</v>
-      </c>
-      <c r="E5" s="45"/>
-      <c r="F5" s="46"/>
+        <v>59 closed Capital trades have generated £153.13 in total P/L. The win rate is 52.5%, while the average win of £10.03 is 1.8x the average loss. Expectancy remains £2.60 per trade, with a maximum drawdown of -£59.95.</v>
+      </c>
+      <c r="E5" s="43"/>
+      <c r="F5" s="44"/>
     </row>
     <row r="6" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
@@ -8509,14 +9083,14 @@
       </c>
       <c r="B6" s="11">
         <f>IFERROR(SUMIF(TradeLog[Outcome (P/L)],"&gt;0",TradeLog[Outcome (P/L)])/COUNTIF(TradeLog[Outcome (P/L)],"&gt;0"),0)</f>
-        <v>11.2036</v>
+        <v>10.025806451612905</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="D6" s="44"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="46"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="44"/>
     </row>
     <row r="7" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
@@ -8524,14 +9098,14 @@
       </c>
       <c r="B7" s="11">
         <f>IFERROR(SUMIF(TradeLog[Outcome (P/L)],"&lt;0",TradeLog[Outcome (P/L)])/COUNTIF(TradeLog[Outcome (P/L)],"&lt;0"),0)</f>
-        <v>-6.4633333333333347</v>
+        <v>-5.6310714285714294</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D7" s="47"/>
-      <c r="E7" s="48"/>
-      <c r="F7" s="49"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="47"/>
     </row>
     <row r="8" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
@@ -8539,16 +9113,16 @@
       </c>
       <c r="B8" s="11">
         <f>(B6*B5)+(B7*(1-B5))</f>
-        <v>2.5504081632653053</v>
+        <v>2.59542372881356</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D8" s="43" t="s">
+      <c r="D8" s="48" t="s">
         <v>103</v>
       </c>
-      <c r="E8" s="43"/>
-      <c r="F8" s="43"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="48"/>
     </row>
     <row r="9" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
@@ -8561,14 +9135,14 @@
       <c r="C9" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D9" s="44" t="str">
+      <c r="D9" s="42" t="str">
         <f>"1. "&amp;IF(B8&gt;0,"Positive expectancy indicates the current trade set has a profitable edge.","Negative expectancy indicates the current approach needs review.")&amp;CHAR(10)&amp;"2. "&amp;IF(B6&gt;ABS(B7),"Average winners exceed average losers, supporting the current payoff profile.","Average losses are at least as large as winners; prioritise loss control and trade selection.")&amp;CHAR(10)&amp;"3. "&amp;IF(B9=0,"Checklist compliance is not yet measured—complete the Yes/No field to assess discipline.","Checklist compliance is "&amp;TEXT(B9,"0.0%")&amp;"; compare compliant and non-compliant results before changing the process.")</f>
         <v>1. Positive expectancy indicates the current trade set has a profitable edge.
 2. Average winners exceed average losers, supporting the current payoff profile.
 3. Checklist compliance is 97.2%; compare compliant and non-compliant results before changing the process.</v>
       </c>
-      <c r="E9" s="45"/>
-      <c r="F9" s="46"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="44"/>
     </row>
     <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
@@ -8576,14 +9150,14 @@
       </c>
       <c r="B10" s="11">
         <f>MIN(0,TradeLog[Drawdown])</f>
-        <v>-55.370000000000019</v>
+        <v>-59.950000000000017</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="D10" s="44"/>
-      <c r="E10" s="45"/>
-      <c r="F10" s="46"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="44"/>
     </row>
     <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
@@ -8591,14 +9165,14 @@
       </c>
       <c r="B11" s="11">
         <f>SUM(TradeLog[Outcome (P/L)])</f>
-        <v>124.96999999999998</v>
+        <v>153.12999999999991</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="D11" s="47"/>
-      <c r="E11" s="48"/>
-      <c r="F11" s="49"/>
+      <c r="D11" s="45"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="47"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -8610,10 +9184,10 @@
     <mergeCell ref="D5:F7"/>
   </mergeCells>
   <conditionalFormatting sqref="B11">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
